--- a/content/data/investigaciones/investigaciones.xlsx
+++ b/content/data/investigaciones/investigaciones.xlsx
@@ -2785,7 +2785,11 @@
           <t>Índice de condiciones de reconciliación en Bogotá D.C.</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>El Índice de Condiciones de Reconciliación en Bogotá D.C., es una herramienta que mide cómo avanza la reconciliación en la ciudad. A partir de dimensiones como cohesión social, inclusión, memoria y cultura política, analiza percepciones y actitudes ciudadanas frente a la convivencia y la paz. Sus resultados orientan decisiones públicas y fortalecen la construcción de confianza y tejido social en Bogotá.</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Sector</t>
@@ -21041,7 +21045,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uvPcjC3VFFwdTN4LKTZqQa4dd_mt6aRq/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1Zr6q_Eutt4lnN9Y6OUXIpAcfFvHJKFJ2/view?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22174,10 +22178,26 @@
       <c r="A651" t="n">
         <v>115</v>
       </c>
-      <c r="B651" t="inlineStr"/>
-      <c r="C651" t="inlineStr"/>
-      <c r="D651" t="inlineStr"/>
-      <c r="E651" t="inlineStr"/>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Informe final</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Informe final </t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1BVdsnc2YA1a2JeXAjjW5O6Z2t0UkP55Z-0WtShl4xa8/edit?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">

--- a/content/data/investigaciones/investigaciones.xlsx
+++ b/content/data/investigaciones/investigaciones.xlsx
@@ -20685,12 +20685,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Informe Festival Monumentum 2025</t>
+          <t>Productos finales Festival Monumentum 2025</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -20700,7 +20700,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UVUUqWPRqoC9-J_3rJPCiwC_FLLGKNPY/view?usp=sharing</t>
+          <t>https://drive.google.com/drive/folders/16LFLVNlKGuWbgTUXHDjiWESjGmAAQM1L?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -20708,51 +20708,19 @@
       <c r="A581" t="n">
         <v>104</v>
       </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>Presentación resultados Festival Monumentum 2025</t>
-        </is>
-      </c>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Xe170cnqUJe0L75fIRULax6fAtG4DoW9/view?usp=sharing</t>
-        </is>
-      </c>
+      <c r="B581" t="inlineStr"/>
+      <c r="C581" t="inlineStr"/>
+      <c r="D581" t="inlineStr"/>
+      <c r="E581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
         <v>104</v>
       </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>Instrumento recolección</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>Formularios Festival Monumentum 2025</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1gnrVe2NjozYAHQCAlLTR23iZjIlgxno0/view?usp=sharing</t>
-        </is>
-      </c>
+      <c r="B582" t="inlineStr"/>
+      <c r="C582" t="inlineStr"/>
+      <c r="D582" t="inlineStr"/>
+      <c r="E582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -20937,12 +20905,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Informe Premio Luis Caballero 2025</t>
+          <t>Productos finales Premio Luis Caballero 2025</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -20952,7 +20920,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18QKMBaJoy4nqZQlFRNYvsZzoo_sFJDIT/view?usp=sharing</t>
+          <t>https://drive.google.com/drive/folders/15KsNtJH-r9FD1xvh9vzNj-9Df_ikXVnD?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -20960,51 +20928,19 @@
       <c r="A593" t="n">
         <v>106</v>
       </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>Presentación resultados Premio Luis Caballero 2025</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1hqNl-FukfRsmkLFkKFbhRMjbCi_keQVa/view?usp=sharing</t>
-        </is>
-      </c>
+      <c r="B593" t="inlineStr"/>
+      <c r="C593" t="inlineStr"/>
+      <c r="D593" t="inlineStr"/>
+      <c r="E593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
         <v>106</v>
       </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>Instrumento recolección</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>Formularios Premio Luis Caballero 2025</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1yzZXgr7VzlUbRtj5fNNi_JyDWjan8aNY/view?usp=sharing</t>
-        </is>
-      </c>
+      <c r="B594" t="inlineStr"/>
+      <c r="C594" t="inlineStr"/>
+      <c r="D594" t="inlineStr"/>
+      <c r="E594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -22205,12 +22141,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Carpeta archivos</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Bases de datos depuras Ciclovía y Escuela de la Bici</t>
+          <t>Informe presentación resultados programas de Ciclovía y Escuela de la bici</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -22220,7 +22156,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1E04LKSNgVLJxshdGwwWy8BQRzbJwMkGs/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1ml0N-5tIACWRSjSXde5tKA2Q9Wn_J-9k/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22230,12 +22166,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Informe presentación resultados programas de Ciclovía y Escuela de la bici</t>
+          <t>Instrumento de recolección Ciclovía 2025</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -22245,7 +22181,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ml0N-5tIACWRSjSXde5tKA2Q9Wn_J-9k/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1uwG-2pHQMS6-t0GhwSTGLJ3fWap6L6Y6/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22255,12 +22191,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Tabla de resultado Escuela de la Bici</t>
+          <t>Instrumento de recolección Escuela de la Bici</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -22270,7 +22206,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1zQZjjzdyGr9BkltBh0Xu5ntzvtJ1siUK/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1j44f0nt3hcD7HjD-Ya48stCgjyv2gPDm/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22305,12 +22241,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Escuela de la Bici</t>
+          <t>Tabla de resultado Escuela de la Bici</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -22320,7 +22256,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j44f0nt3hcD7HjD-Ya48stCgjyv2gPDm/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1zQZjjzdyGr9BkltBh0Xu5ntzvtJ1siUK/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22330,12 +22266,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Ciclovía 2025</t>
+          <t>Bases de datos depuras Ciclovía y Escuela de la Bici</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -22345,7 +22281,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uwG-2pHQMS6-t0GhwSTGLJ3fWap6L6Y6/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1E04LKSNgVLJxshdGwwWy8BQRzbJwMkGs/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22584,12 +22520,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Informe Festival de Verano 2025</t>
+          <t>Productos finales Festival de Verano 2025</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -22599,7 +22535,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1flNJJ6CFGtqXgQG3sAJJHbyuCFh8RuOs/view?usp=sharing</t>
+          <t>https://drive.google.com/drive/folders/14Ap2CtsPvGqgr55CTIh_z0MO3XnfklKi?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22607,26 +22543,10 @@
       <c r="A671" t="n">
         <v>119</v>
       </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>Instrumento recolección</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>Formularios Festival de Verano 2025</t>
-        </is>
-      </c>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1syhJzh5ipnYrYWpHmXhOuq1UKOuyL5FQ/view?usp=sharing</t>
-        </is>
-      </c>
+      <c r="B671" t="inlineStr"/>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -22772,12 +22692,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Instrucciones sobre registro de información</t>
+          <t>Tablero Encuesta</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -22787,7 +22707,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gbIyrWH8cK07q00yoPBs9D8IWYNv4P2I/view?usp=drive_link</t>
+          <t>https://lookerstudio.google.com/reporting/ccbecff5-f250-4a21-b1f8-5290632c1187/page/p_shhgwuepsd</t>
         </is>
       </c>
     </row>
@@ -22797,12 +22717,12 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Prototipo para registro</t>
+          <t>Instrucciones sobre registro de información</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -22812,7 +22732,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>https://www.prototipos-sicc.com/app/barrios_vivos/explorar</t>
+          <t>https://drive.google.com/file/d/1gbIyrWH8cK07q00yoPBs9D8IWYNv4P2I/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22822,12 +22742,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Tablero de seguimiento</t>
+          <t>Prototipo para registro</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -22837,7 +22757,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>https://lookerstudio.google.com/reporting/a1e266a6-ed1a-4500-8776-58e82d1d7746/page/p_pjg06p6njd</t>
+          <t>https://www.prototipos-sicc.com/app/barrios_vivos/explorar</t>
         </is>
       </c>
     </row>
@@ -22847,12 +22767,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Audiovisual</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Vídeo tutoriales para registro</t>
+          <t>Tablero de seguimiento</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -22862,7 +22782,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1Cuy0w3cr883zTx_4X1n4TquCUCnheBRm</t>
+          <t>https://lookerstudio.google.com/reporting/a1e266a6-ed1a-4500-8776-58e82d1d7746/page/p_pjg06p6njd</t>
         </is>
       </c>
     </row>
@@ -22872,12 +22792,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Audiovisual</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Tablero Encuesta</t>
+          <t>Vídeo tutoriales para registro</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -22887,7 +22807,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>https://lookerstudio.google.com/reporting/ccbecff5-f250-4a21-b1f8-5290632c1187/page/p_shhgwuepsd</t>
+          <t>https://drive.google.com/drive/folders/1Cuy0w3cr883zTx_4X1n4TquCUCnheBRm</t>
         </is>
       </c>
     </row>

--- a/content/data/investigaciones/investigaciones.xlsx
+++ b/content/data/investigaciones/investigaciones.xlsx
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EBC - LEO 2025</t>
+          <t>EBC - Encuesta de Lectura, Escritura y Oralidad 2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Lectura - Escritura - Oralidad -EBC</t>
+          <t>lectura, bibliotecas, oralidad, podcast, libros, escritura, espacios de lectura, virgilio barco, bibliored</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -8615,7 +8615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E730"/>
+  <dimension ref="A1:E732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21732,16 +21732,16 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Espacios de Lectura</t>
+          <t>Tabero de Resultados</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -21751,22 +21751,22 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16W6G5tRSMAk7F6SDasy_0yM92zpbwTbq/view?usp=drive_link</t>
+          <t>https://observatoriocultura.github.io/observatorio/#/ebc/lectura-escritura-y-oralidad-2025</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Usaquén - Servitá</t>
+          <t>Base de datos detallada</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FRWQBJGGoZZttLVMLwagnXXYShR2lFqi/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1ncjBs9trvq52fX5STxFHJTkdM7tQLgc6/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -21786,12 +21786,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública La Peña</t>
+          <t>Instrumento de recolección Espacios de Lectura</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RwsGRlcn7XYuXJ1rtmYJUnWj69aEpyMV/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/16W6G5tRSMAk7F6SDasy_0yM92zpbwTbq/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21816,7 +21816,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública FUGA</t>
+          <t>Sondeo Visitantes Biblioteca Pública Usaquén - Servitá</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DYP4zsQhzkx8PH-yydqgAloHd_DCEsTV/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1FRWQBJGGoZZttLVMLwagnXXYShR2lFqi/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21841,7 +21841,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Virgilio Barco</t>
+          <t>Sondeo Visitantes Biblioteca Pública La Peña</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1caNM182qy71k48IqO5Mzv168P1KIbDs-/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1RwsGRlcn7XYuXJ1rtmYJUnWj69aEpyMV/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21866,7 +21866,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Caros E. Restrepo</t>
+          <t>Sondeo Visitantes Biblioteca Pública FUGA</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19dgvioy6RYxY0oUSvS7HrWGkCn6Bdcve/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1DYP4zsQhzkx8PH-yydqgAloHd_DCEsTV/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21891,7 +21891,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Francisco José de Caldas</t>
+          <t>Sondeo Visitantes Biblioteca Pública Virgilio Barco</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Xdo-9N2TnWtBpoKVhiMIb3Cwj2SYmDWR/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1caNM182qy71k48IqO5Mzv168P1KIbDs-/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21916,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Gabriel García Márquez - El Tunal</t>
+          <t>Sondeo Visitantes Biblioteca Pública Caros E. Restrepo</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-_wpdpR7e4SMEdEdCVZQNFsVSxxFf7Yn/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/19dgvioy6RYxY0oUSvS7HrWGkCn6Bdcve/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21941,7 +21941,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Julio Mario Santodomingo</t>
+          <t>Sondeo Visitantes Biblioteca Pública Francisco José de Caldas</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -21951,7 +21951,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19-EGROjB7Se6H5BC7lQ-5kcioDv17Aj8/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1Xdo-9N2TnWtBpoKVhiMIb3Cwj2SYmDWR/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21966,7 +21966,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Manuel Zapata Olivella - El Tintal</t>
+          <t>Sondeo Visitantes Biblioteca Pública Gabriel García Márquez - El Tunal</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1smpXVkZNK0D0NVvXTpaToUpQYbnUsJ2X/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1-_wpdpR7e4SMEdEdCVZQNFsVSxxFf7Yn/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21984,14 +21984,30 @@
       <c r="A645" t="n">
         <v>114</v>
       </c>
-      <c r="B645" t="inlineStr"/>
-      <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr"/>
-      <c r="E645" t="inlineStr"/>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Informe final</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Sondeo Visitantes Biblioteca Pública Julio Mario Santodomingo</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/19-EGROjB7Se6H5BC7lQ-5kcioDv17Aj8/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -22000,7 +22016,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Informe Espacios de actividad física</t>
+          <t>Sondeo Visitantes Biblioteca Pública Manuel Zapata Olivella - El Tintal</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -22008,57 +22024,33 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="E646" t="inlineStr"/>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1smpXVkZNK0D0NVvXTpaToUpQYbnUsJ2X/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>115</v>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>Presentación resultados programas de Espacios de actividad física</t>
-        </is>
-      </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E647" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1qlsGIDoE8xuZRs0DD2wbob15tro_VEMX/view?usp=drive_link</t>
-        </is>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B647" t="inlineStr"/>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr"/>
+      <c r="E647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
         <v>115</v>
       </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>Informe cuantitativo</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>Tablas de resultado Espacios de actividad física</t>
-        </is>
-      </c>
+      <c r="B648" t="inlineStr"/>
+      <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E648" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/spreadsheets/d/1PeAnosF7Ne2O-rSJHyJNPYU_8VyKObOM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
-        </is>
-      </c>
+      <c r="E648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -22066,22 +22058,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Base de datos Espacios de actividad física</t>
+          <t>Presentación resultados programas de Espacios de actividad física</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1pkjosapWgOR6hhHYZF-HqbqKBJZlYhtM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1qlsGIDoE8xuZRs0DD2wbob15tro_VEMX/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22083,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Espacios de actividad física</t>
+          <t>Tablas de resultado Espacios de actividad física</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -22106,7 +22098,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1u4nc5ifpincy8njQifsXd-QfzDxYlwR8/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1PeAnosF7Ne2O-rSJHyJNPYU_8VyKObOM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22116,12 +22108,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Informe final </t>
+          <t>Base de datos Espacios de actividad física</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -22131,22 +22123,22 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1BVdsnc2YA1a2JeXAjjW5O6Z2t0UkP55Z-0WtShl4xa8/edit?usp=sharing</t>
+          <t>https://docs.google.com/spreadsheets/d/1pkjosapWgOR6hhHYZF-HqbqKBJZlYhtM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Informe presentación resultados programas de Ciclovía y Escuela de la bici</t>
+          <t>Instrumento de recolección Espacios de actividad física</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -22156,22 +22148,22 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ml0N-5tIACWRSjSXde5tKA2Q9Wn_J-9k/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1u4nc5ifpincy8njQifsXd-QfzDxYlwR8/view?usp=drive_link</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Ciclovía 2025</t>
+          <t>Informe final Espacios de actividad física</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -22181,7 +22173,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uwG-2pHQMS6-t0GhwSTGLJ3fWap6L6Y6/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1VMhbyOIs4ScBC_JIaaLKz8_A-A7G5cOl/view?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22191,12 +22183,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Escuela de la Bici</t>
+          <t>Informe presentación resultados programas de Ciclovía y Escuela de la bici</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -22206,7 +22198,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j44f0nt3hcD7HjD-Ya48stCgjyv2gPDm/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1ml0N-5tIACWRSjSXde5tKA2Q9Wn_J-9k/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22216,12 +22208,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Tabla de resultado Ciclovía 2025</t>
+          <t>Instrumento de recolección Ciclovía 2025</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -22231,7 +22223,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/16ZpRSW0DGRb8JPE9QCzrLu2VyFN2IXTt/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1uwG-2pHQMS6-t0GhwSTGLJ3fWap6L6Y6/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22233,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Tabla de resultado Escuela de la Bici</t>
+          <t>Instrumento de recolección Escuela de la Bici</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -22256,7 +22248,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1zQZjjzdyGr9BkltBh0Xu5ntzvtJ1siUK/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1j44f0nt3hcD7HjD-Ya48stCgjyv2gPDm/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22266,12 +22258,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Carpeta archivos</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Bases de datos depuras Ciclovía y Escuela de la Bici</t>
+          <t>Tabla de resultado Ciclovía 2025</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -22281,22 +22273,22 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1E04LKSNgVLJxshdGwwWy8BQRzbJwMkGs/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/16ZpRSW0DGRb8JPE9QCzrLu2VyFN2IXTt/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Docuento metodológico</t>
+          <t>Tabla de resultado Escuela de la Bici</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -22306,22 +22298,22 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aRQvwNu04n8HAXbE9o69GhoBogD2Uqj6/view?usp=sharing</t>
+          <t>https://docs.google.com/spreadsheets/d/1zQZjjzdyGr9BkltBh0Xu5ntzvtJ1siUK/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Instrumento de recolección</t>
+          <t>Bases de datos depuras Ciclovía y Escuela de la Bici</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -22331,7 +22323,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1VZIqZvzrUOBhPEVGF_n98ZthOb8RmV4V/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1E04LKSNgVLJxshdGwwWy8BQRzbJwMkGs/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22341,12 +22333,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Matriz de revisión de literatura</t>
+          <t>Docuento metodológico</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -22356,7 +22348,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U5vso-3VmBTA0uPp6Jwz3zolvbWR17sT/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1aRQvwNu04n8HAXbE9o69GhoBogD2Uqj6/view?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22366,13 +22358,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matriz de tipología de actores
-</t>
+          <t>Instrumento de recolección</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -22382,7 +22373,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HQUAEOPZWxBtWc-dexksGmXsqH3VLyB3/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1VZIqZvzrUOBhPEVGF_n98ZthOb8RmV4V/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22397,7 +22388,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Matriz de esquema interpretativo de la gobernanza del deporte</t>
+          <t>Matriz de revisión de literatura</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -22407,7 +22398,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16EFX41hHQvz_pSfEG86A1RV2KQ969hzt/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1U5vso-3VmBTA0uPp6Jwz3zolvbWR17sT/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22417,37 +22408,38 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Anexo</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t xml:space="preserve">Matriz de tipología de actores
+</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1t70D31QSK9xXUEgVSMhUzuwxOwgYAfyO/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1HQUAEOPZWxBtWc-dexksGmXsqH3VLyB3/view?usp=drive_link</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Anexo</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Formulario EBC - PACCP Final</t>
+          <t>Matriz de esquema interpretativo de la gobernanza del deporte</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -22457,22 +22449,34 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1qsclq1ogNVWTc6Sh7swGgV-k7DZr-Wnj/edit?usp=drive_link&amp;ouid=105090632649587320414&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/16EFX41hHQvz_pSfEG86A1RV2KQ969hzt/view?usp=drive_link</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr"/>
+          <t>Plan de trabajo</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Plan de trabajo</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1t70D31QSK9xXUEgVSMhUzuwxOwgYAfyO/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -22480,18 +22484,34 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
-      <c r="E666" t="inlineStr"/>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Formulario EBC - PACCP Final</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1qsclq1ogNVWTc6Sh7swGgV-k7DZr-Wnj/edit?usp=drive_link&amp;ouid=105090632649587320414&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
         <v>118</v>
       </c>
-      <c r="B667" t="inlineStr"/>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr"/>
@@ -22500,7 +22520,11 @@
       <c r="A668" t="n">
         <v>118</v>
       </c>
-      <c r="B668" t="inlineStr"/>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Informe cuantitativo</t>
+        </is>
+      </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr"/>
       <c r="E668" t="inlineStr"/>
@@ -22516,32 +22540,16 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>119</v>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>Carpeta archivos</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>Productos finales Festival de Verano 2025</t>
-        </is>
-      </c>
-      <c r="D670" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/14Ap2CtsPvGqgr55CTIh_z0MO3XnfklKi?usp=sharing</t>
-        </is>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B670" t="inlineStr"/>
+      <c r="C670" t="inlineStr"/>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr"/>
@@ -22552,10 +22560,26 @@
       <c r="A672" t="n">
         <v>119</v>
       </c>
-      <c r="B672" t="inlineStr"/>
-      <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
-      <c r="E672" t="inlineStr"/>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Carpeta archivos</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Productos finales Festival de Verano 2025</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/14Ap2CtsPvGqgr55CTIh_z0MO3XnfklKi?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -22586,53 +22610,21 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>120</v>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>Carpeta archivos</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>Productos finales Concurso Internacional de Violín 2025</t>
-        </is>
-      </c>
-      <c r="D676" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/114QuIa8ZzjC_GNjRUVggtFVTN3y_zOAL?usp=sharing</t>
-        </is>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B676" t="inlineStr"/>
+      <c r="C676" t="inlineStr"/>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>120</v>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>Carpeta archivos</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>Productos finales Bienal Internacional de Arte y Ciudad BOG25</t>
-        </is>
-      </c>
-      <c r="D677" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/17Bi6a6nKxYmJNqTEWtIH6lYiXMxIECYi?usp=sharing</t>
-        </is>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B677" t="inlineStr"/>
+      <c r="C677" t="inlineStr"/>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -22645,7 +22637,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Productos finales Navidad es Cultura 2025</t>
+          <t>Productos finales Concurso Internacional de Violín 2025</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -22655,7 +22647,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1rb7lrObK-r5g1iF6SsaYKbR-J_K7nLy-?usp=sharing</t>
+          <t>https://drive.google.com/drive/folders/114QuIa8ZzjC_GNjRUVggtFVTN3y_zOAL?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22663,19 +22655,51 @@
       <c r="A679" t="n">
         <v>120</v>
       </c>
-      <c r="B679" t="inlineStr"/>
-      <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
-      <c r="E679" t="inlineStr"/>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Carpeta archivos</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Productos finales Bienal Internacional de Arte y Ciudad BOG25</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/17Bi6a6nKxYmJNqTEWtIH6lYiXMxIECYi?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
         <v>120</v>
       </c>
-      <c r="B680" t="inlineStr"/>
-      <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
-      <c r="E680" t="inlineStr"/>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Carpeta archivos</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Productos finales Navidad es Cultura 2025</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1rb7lrObK-r5g1iF6SsaYKbR-J_K7nLy-?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -22688,53 +22712,21 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>121</v>
-      </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>Visualización</t>
-        </is>
-      </c>
-      <c r="C682" t="inlineStr">
-        <is>
-          <t>Tablero Encuesta</t>
-        </is>
-      </c>
-      <c r="D682" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr">
-        <is>
-          <t>https://lookerstudio.google.com/reporting/ccbecff5-f250-4a21-b1f8-5290632c1187/page/p_shhgwuepsd</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" t="inlineStr"/>
+      <c r="D682" t="inlineStr"/>
+      <c r="E682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>121</v>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C683" t="inlineStr">
-        <is>
-          <t>Instrucciones sobre registro de información</t>
-        </is>
-      </c>
-      <c r="D683" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1gbIyrWH8cK07q00yoPBs9D8IWYNv4P2I/view?usp=drive_link</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B683" t="inlineStr"/>
+      <c r="C683" t="inlineStr"/>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -22742,12 +22734,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Prototipo para registro</t>
+          <t>Tablero Encuesta</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -22757,7 +22749,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>https://www.prototipos-sicc.com/app/barrios_vivos/explorar</t>
+          <t>https://lookerstudio.google.com/reporting/ccbecff5-f250-4a21-b1f8-5290632c1187/page/p_shhgwuepsd</t>
         </is>
       </c>
     </row>
@@ -22767,12 +22759,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Tablero de seguimiento</t>
+          <t>Instrucciones sobre registro de información</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -22782,7 +22774,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>https://lookerstudio.google.com/reporting/a1e266a6-ed1a-4500-8776-58e82d1d7746/page/p_pjg06p6njd</t>
+          <t>https://drive.google.com/file/d/1gbIyrWH8cK07q00yoPBs9D8IWYNv4P2I/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22792,12 +22784,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Audiovisual</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Vídeo tutoriales para registro</t>
+          <t>Prototipo para registro</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -22807,22 +22799,22 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1Cuy0w3cr883zTx_4X1n4TquCUCnheBRm</t>
+          <t>https://www.prototipos-sicc.com/app/barrios_vivos/explorar</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Tablero de seguimiento</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -22832,22 +22824,22 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1f6sPy_pAB5aZpB_kvra4Qy4YiKsiGjgR/view?usp=drive_link</t>
+          <t>https://lookerstudio.google.com/reporting/a1e266a6-ed1a-4500-8776-58e82d1d7746/page/p_pjg06p6njd</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Audiovisual</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Vídeo tutoriales para registro</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -22857,22 +22849,22 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>https://docs.google.com/presentation/d/1BogTIIMdH15s1-pa4Z9qN-RIW_VTct_g/edit?slide=id.p1#slide=id.p1</t>
+          <t>https://drive.google.com/drive/folders/1Cuy0w3cr883zTx_4X1n4TquCUCnheBRm</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Anexo resultados comparativos</t>
+          <t>Presentación final</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -22882,17 +22874,17 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/11YGZTE7pzMI4lDBZmvYiq5Xq9TwCE1z4/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1f6sPy_pAB5aZpB_kvra4Qy4YiKsiGjgR/view?usp=drive_link</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Infografía</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -22907,30 +22899,34 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VhroKpPxgqcqQso3fwqBLmJ5zbwmJ8od/view?usp=share_link</t>
+          <t>https://docs.google.com/presentation/d/1BogTIIMdH15s1-pa4Z9qN-RIW_VTct_g/edit?slide=id.p1#slide=id.p1</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Anexo</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Diseño de experimento económico</t>
+          <t>Anexo resultados comparativos</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E691" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/11YGZTE7pzMI4lDBZmvYiq5Xq9TwCE1z4/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -22938,20 +22934,24 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Infografía</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Cálculo de consumo de agua en ducha por factura</t>
+          <t>Presentación final</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E692" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1VhroKpPxgqcqQso3fwqBLmJ5zbwmJ8od/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -22959,12 +22959,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Datos EAAB por Barrio para experimento</t>
+          <t>Diseño de experimento económico</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -22980,12 +22980,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Infografía</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Datos de hitos Barrios Vivos Agua</t>
+          <t>Cálculo de consumo de agua en ducha por factura</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -23001,12 +23001,12 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Cronograma Investigación Agua</t>
+          <t>Datos EAAB por Barrio para experimento</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -23018,41 +23018,37 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Infografía</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Datos de hitos Barrios Vivos Agua</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E696" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1KnbyFYzDxdGfLHJqZDXjhrrUnvwF8O0D/view?usp=share_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Tablas de salida</t>
+          <t>Cronograma Investigación Agua</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -23068,12 +23064,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Carpeta archivos</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>ICC Distritos Creativos 2025</t>
+          <t>Presentación final</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -23081,7 +23077,11 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="E698" t="inlineStr"/>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1KnbyFYzDxdGfLHJqZDXjhrrUnvwF8O0D/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -23089,17 +23089,17 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Formulario ICC Distritos Creativos 2025</t>
+          <t>Tablas de salida</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
@@ -23110,33 +23110,33 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Cronograma ICC Distritos Creativos</t>
+          <t>ICC Distritos Creativos 2025</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Informe de caracterización con fuentes secundarias</t>
+          <t>Formulario ICC Distritos Creativos 2025</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -23144,40 +23144,32 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="E701" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1nqXIcpjznaD1Dn8fjBR_fg7L2XdFwKsg/view?usp=share_link</t>
-        </is>
-      </c>
+      <c r="E701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tablero de recorrido por espacio púbilco del centro </t>
+          <t>Cronograma ICC Distritos Creativos</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E702" t="inlineStr">
-        <is>
-          <t>https://sdcrd.maps.arcgis.com/apps/dashboards/f5ba03060ca94dfa8d4fee25f0de6d7f</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
@@ -23186,28 +23178,32 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tablero de recorrido por espacio púbilco del centro </t>
+          <t>Informe de caracterización con fuentes secundarias</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E703" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1nqXIcpjznaD1Dn8fjBR_fg7L2XdFwKsg/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t xml:space="preserve">Tablero de recorrido por espacio púbilco del centro </t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -23217,34 +23213,30 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NsVGUlWsADXoKnEO31ub8Cp0Krp9Aig3/view?usp=drive_link</t>
+          <t>https://sdcrd.maps.arcgis.com/apps/dashboards/f5ba03060ca94dfa8d4fee25f0de6d7f</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Anexo de definición</t>
+          <t xml:space="preserve">Tablero de recorrido por espacio púbilco del centro </t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E705" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1yZIHrgUGq2Lu0TFlzzyGvCS7RXjuxd1M/view?usp=drive_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -23252,12 +23244,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Formulario sondeo</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -23267,7 +23259,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AVJBnJQld7Uyna3WW04TEPkFOQQqFlQl/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1NsVGUlWsADXoKnEO31ub8Cp0Krp9Aig3/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -23275,19 +23267,51 @@
       <c r="A707" t="n">
         <v>128</v>
       </c>
-      <c r="B707" t="inlineStr"/>
-      <c r="C707" t="inlineStr"/>
-      <c r="D707" t="inlineStr"/>
-      <c r="E707" t="inlineStr"/>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Anexo</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Anexo de definición</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1yZIHrgUGq2Lu0TFlzzyGvCS7RXjuxd1M/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
         <v>128</v>
       </c>
-      <c r="B708" t="inlineStr"/>
-      <c r="C708" t="inlineStr"/>
-      <c r="D708" t="inlineStr"/>
-      <c r="E708" t="inlineStr"/>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Formulario sondeo</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1AVJBnJQld7Uyna3WW04TEPkFOQQqFlQl/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -23300,62 +23324,34 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>129</v>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Informe final</t>
-        </is>
-      </c>
-      <c r="C710" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Análisis de impacto de la implementación de los Laboratorios de Bienestar a adolescentes: Comparación de encuestas pre y post de la implementación del laboratorio: “El Viaje Hacia Dentro de Mi” - Estrategia EstarBien Bogotá </t>
-        </is>
-      </c>
-      <c r="D710" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E710" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1R8tXuWA5XQrs_U1P2LAakV8WjHZp-Hyc/view?usp=share_link</t>
-        </is>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B710" t="inlineStr"/>
+      <c r="C710" t="inlineStr"/>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>129</v>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Plan de trabajo</t>
-        </is>
-      </c>
-      <c r="C711" t="inlineStr">
-        <is>
-          <t>Plan de investigación</t>
-        </is>
-      </c>
-      <c r="D711" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B711" t="inlineStr"/>
+      <c r="C711" t="inlineStr"/>
+      <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Matriz de preguntas de la EBC</t>
+          <t xml:space="preserve">Análisis de impacto de la implementación de los Laboratorios de Bienestar a adolescentes: Comparación de encuestas pre y post de la implementación del laboratorio: “El Viaje Hacia Dentro de Mi” - Estrategia EstarBien Bogotá </t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -23365,38 +23361,34 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
+          <t>https://drive.google.com/file/d/1R8tXuWA5XQrs_U1P2LAakV8WjHZp-Hyc/view?usp=share_link</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Plan de investigación</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Ez5bU0fGKborxl5_zyUc27muZZizMtFC/view?usp=share_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
@@ -23405,28 +23397,32 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Encuesta de recolección de fuentes primarias</t>
+          <t>Matriz de preguntas de la EBC</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E714" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Cultura Metro - Estado del Arte</t>
+          <t>Presentación final</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -23436,52 +23432,80 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1TvqbXkunNvyWYuMDu2TZ_rwJeAI2fjFR/edit?usp=sharing&amp;ouid=100772003525119686921&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1Ez5bU0fGKborxl5_zyUc27muZZizMtFC/view?usp=share_link</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presentación Final </t>
+          <t>Encuesta de recolección de fuentes primarias</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E716" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/16AYD-Y9HF8O45rYDxH6a_pgEbUjv_Ofo/view?usp=drive_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>134</v>
-      </c>
-      <c r="B717" t="inlineStr"/>
-      <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Informe final</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Cultura Metro - Estado del Arte</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1TvqbXkunNvyWYuMDu2TZ_rwJeAI2fjFR/edit?usp=sharing&amp;ouid=100772003525119686921&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>134</v>
-      </c>
-      <c r="B718" t="inlineStr"/>
-      <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
-      <c r="E718" t="inlineStr"/>
+        <v>133</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Presentación</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presentación Final </t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16AYD-Y9HF8O45rYDxH6a_pgEbUjv_Ofo/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -23514,80 +23538,48 @@
       <c r="A722" t="n">
         <v>134</v>
       </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>Visualización</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>Tablero invitados ECCI 2025 - Seguimiento</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>https://lookerstudio.google.com/reporting/49195a24-bd9a-4773-af8a-966bb697f78b/page/p_pjg06p6njd</t>
-        </is>
-      </c>
+      <c r="B722" t="inlineStr"/>
+      <c r="C722" t="inlineStr"/>
+      <c r="D722" t="inlineStr"/>
+      <c r="E722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>135</v>
-      </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>Informe final</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>Marco conceptual</t>
-        </is>
-      </c>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/12I-YN44-_0suC2dpHX3vOLYgHwHTHA-E/view?usp=share_link</t>
-        </is>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B723" t="inlineStr"/>
+      <c r="C723" t="inlineStr"/>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t xml:space="preserve">índice de reconciliación y paz </t>
+          <t>Tablero invitados ECCI 2025 - Seguimiento</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ySdEC1LyX43LPMZdqi2vBiSWXoQRieJH/view?usp=share_link</t>
+          <t>https://lookerstudio.google.com/reporting/49195a24-bd9a-4773-af8a-966bb697f78b/page/p_pjg06p6njd</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
@@ -23596,30 +23588,32 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documento Desarrollo Técnico Normativo y misional del enfoque de Cultura Ciudadana para la movilidad
-</t>
+          <t>Marco conceptual</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E725" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12I-YN44-_0suC2dpHX3vOLYgHwHTHA-E/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estado del arte y de la práctica sobre problemáticas relacionadas a cultura ciudadana y movilidad 
-</t>
+          <t xml:space="preserve">índice de reconciliación y paz </t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -23629,7 +23623,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l3CBDIXbCVbiG153wP35kkD4Q44DZbI1/view?usp=share_link</t>
+          <t>https://drive.google.com/file/d/1ySdEC1LyX43LPMZdqi2vBiSWXoQRieJH/view?usp=share_link</t>
         </is>
       </c>
     </row>
@@ -23639,12 +23633,13 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Mapa/Geovisor</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Geovisor Movilidad</t>
+          <t xml:space="preserve">Documento Desarrollo Técnico Normativo y misional del enfoque de Cultura Ciudadana para la movilidad
+</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -23652,15 +23647,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr">
-        <is>
-          <t>https://www.arcgis.com/apps/dashboards/3a8a858de18047528174d7bc158b4b42</t>
-        </is>
-      </c>
+      <c r="E727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
@@ -23669,7 +23660,8 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Informe final de mediciones</t>
+          <t xml:space="preserve">Estado del arte y de la práctica sobre problemáticas relacionadas a cultura ciudadana y movilidad 
+</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -23679,32 +23671,32 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1liHn1t_9w1D5ry0UIfT6kxLszVuyErB_/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1l3CBDIXbCVbiG153wP35kkD4Q44DZbI1/view?usp=share_link</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Mapa/Geovisor</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Tablero de resultados</t>
+          <t>Geovisor Movilidad</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>https://app.powerbi.com/view?r=eyJrIjoiOWYwOThhMjMtOTBjZC00ZGY5LThhYjktMTY5OWYzYWI0ZDJjIiwidCI6IjRmNzkzOWM3LWFhNjAtNDliZC05YjdiLTZmODFjMzdkMWIzNyJ9&amp;pageName=ef377ed828063259b15e</t>
+          <t>https://www.arcgis.com/apps/dashboards/3a8a858de18047528174d7bc158b4b42</t>
         </is>
       </c>
     </row>
@@ -23714,20 +23706,70 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
+          <t>Informe final</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Informe final de mediciones</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1liHn1t_9w1D5ry0UIfT6kxLszVuyErB_/view?usp=drive_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>137</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Visualización</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Tablero de resultados</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>https://app.powerbi.com/view?r=eyJrIjoiOWYwOThhMjMtOTBjZC00ZGY5LThhYjktMTY5OWYzYWI0ZDJjIiwidCI6IjRmNzkzOWM3LWFhNjAtNDliZC05YjdiLTZmODFjMzdkMWIzNyJ9&amp;pageName=ef377ed828063259b15e</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>137</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
           <t>Base de datos</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>Datos de encuestas</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E730" t="inlineStr">
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1rX2RfuDon4SukoBpHxRg7m9fnL6_1Jw2/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
         </is>

--- a/content/data/investigaciones/investigaciones.xlsx
+++ b/content/data/investigaciones/investigaciones.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:T137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,10 +493,40 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>investigadores</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>cantidad_productos</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>cantidad_radicados</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>cantidad_hallazgos</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>cantidad_paginas</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>fecha_socializacion</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
@@ -561,44 +591,66 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Mábel Ayala, Mauricio Ojeda</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>108</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>8/8/2025</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sondeo sobre el Programa Libro al Viento</t>
+          <t>EBC - Encuesta de Lectura, Escritura y Oralidad 2025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Análisis de los usos sociales del Programa Libro al Viento en Bogotá, a partir de un enfoque mixto que combina herramientas cuantitativas y cualitativas para comprender las prácticas de lectura en el espacio público. El estudio se centra en las formas de conocimiento, apropiación y circulación de los libros, así como en los sentidos que la ciudadanía atribuye al programa en su vida cotidiana. Los resultados permiten caracterizar a Libro al Viento como una experiencia de encuentro con la lectura integrada a la dinámica urbana, e identificar tanto sus aportes simbólicos como los principales retos para su visibilidad y sostenibilidad.</t>
+          <t>Diseño, aplicación y análisis del módulo de Lectura, Escritura y Oralidad en la Encuesta Bienal de Culturas 2025, en articulación con la Dirección de Lectura y Bibliotecas. Incluye trabajo de campo por muestreo probabilístico, procesamiento de datos y análisis de resultados.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IDARTES</t>
+          <t>SCRD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>202591004200100008E</t>
+          <t>202591004200100016E</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IDARTES G Literatura</t>
+          <t>SCCGC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -610,51 +662,77 @@
           <t>Sector Cultura</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Obtener información que permita hacer seguimiento a la política pública LEO y caracterizar los hábitos de lectura, escritura y oralidad. Recoge los conocimientos, actitudes, valoraciones, emociones y percepciones frente a la lectura, la escritura y la oralidad.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1m2paVRCF0WLmM6GCJXbDKsrppfiwtB73</t>
+          <t>https://drive.google.com/drive/folders/1sTNCho5MGwcW5BVNJa4KYzMzVgdYCLeG</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>lectura, literatura, aniversario, leo, Libro al Viento; lectura en el espacio público; usos sociales de la lectura; apropiación simbólica; políticas culturales; circulación de libros.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Carlos Suárez, Giovani Moreno</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+          <t>lectura, bibliotecas, oralidad, podcast, libros, escritura, espacios de lectura, virgilio barco, bibliored</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Viviana Rodríguez, Carlos Suárez, Giovani Moreno, Laura Lozano</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>126</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cultura ciudadana en TransMilenio: confianza y orgullo</t>
+          <t>Sondeo sobre el Programa Libro al Viento</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medición de las percepciones ciudadanas de confianza, orgullo y apropiación en el sistema TransMilenio. A partir de una encuesta aplicada a personas usuarias en estaciones y portales priorizados, el estudio analiza estas dimensiones junto con emociones y comportamientos asociados al uso del sistema, con el objetivo de generar evidencia para comprender la experiencia cotidiana, evaluar procesos de transformación cultural y orientar acciones de cultura ciudadana basadas en datos.</t>
+          <t>Análisis de los usos sociales del Programa Libro al Viento en Bogotá, a partir de un enfoque mixto que combina herramientas cuantitativas y cualitativas para comprender las prácticas de lectura en el espacio público. El estudio se centra en las formas de conocimiento, apropiación y circulación de los libros, así como en los sentidos que la ciudadanía atribuye al programa en su vida cotidiana. Los resultados permiten caracterizar a Libro al Viento como una experiencia de encuentro con la lectura integrada a la dinámica urbana, e identificar tanto sus aportes simbólicos como los principales retos para su visibilidad y sostenibilidad.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>IDARTES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>202591004200100027E</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>202591004200100008E</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IDARTES G Literatura</t>
+        </is>
+      </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
@@ -665,22 +743,48 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cultura Ciudadana</t>
+          <t>Sector Cultura</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1Oevcfhqb2fsyzMSPchXqH7WxkIbqvNw_</t>
+          <t>https://drive.google.com/drive/folders/1m2paVRCF0WLmM6GCJXbDKsrppfiwtB73</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>transporte, movilidad, transmilenio, estaciones, colados, confianza, orgullo, apropiación, confianza en TransMilenio, orgullo ciudadano, apropiación del sistema de transporte, cultura ciudadana Bogotá, percepción ciudadana transporte público, convivencia en TransMilenio, emociones y comportamiento ciudadano, investigación cultura ciudadana, medición de percepción ciudadana, transformación cultural urbana</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+          <t>lectura, literatura, aniversario, leo, Libro al Viento; lectura en el espacio público; usos sociales de la lectura; apropiación simbólica; políticas culturales; circulación de libros.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Carlos Suárez, Giovani Moreno</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>163</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -738,7 +842,25 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>17</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -797,10 +919,32 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>InventarioBogotá</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Jhonatan Rosas</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>55</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -850,41 +994,51 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caracterización de Entidades Sin Ánimo de Lucro 2025</t>
+          <t>Cultura ciudadana en TransMilenio: confianza y orgullo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Segunda etapa del estudio sectorial iniciado en 2024, enfocado en actualizar y profundizar la caracterización de las Entidades Sin Ánimo de Lucro (ESAL) adscritas a la SCRD, abordando aspectos de infraestructura, oferta de valor, sostenibilidad financiera y modelos de gestión.</t>
+          <t>Medición de las percepciones ciudadanas de confianza, orgullo y apropiación en el sistema TransMilenio. A partir de una encuesta aplicada a personas usuarias en estaciones y portales priorizados, el estudio analiza estas dimensiones junto con emociones y comportamientos asociados al uso del sistema, con el objetivo de generar evidencia para comprender la experiencia cotidiana, evaluar procesos de transformación cultural y orientar acciones de cultura ciudadana basadas en datos.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SCRD</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>202591004200100004E</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gobernanza - DPJ</t>
-        </is>
-      </c>
+          <t>202591004200100027E</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -893,31 +1047,40 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sector Cultura</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Realizar un análisis de la información recolectada en los formularios aplicados a las ESALES 2024 y 2025, en términos de oferta de valor, estructura organizacional y herramientas de sostenibilidad.
-</t>
-        </is>
-      </c>
+          <t>Cultura Ciudadana</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1GPyUMdbxqqJ-fja7DNFswVLKyoucNKao</t>
+          <t>https://drive.google.com/drive/folders/1Oevcfhqb2fsyzMSPchXqH7WxkIbqvNw_</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Dirección de Personas Juridicas, ESALES Culturales, Oferta de Valor, Infraestructura, Sostenibilidad, economía</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Giovani Moreno,Carlos Suárez </t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+          <t>transporte, movilidad, transmilenio, estaciones, colados, confianza, orgullo, apropiación, confianza en TransMilenio, orgullo ciudadano, apropiación del sistema de transporte, cultura ciudadana Bogotá, percepción ciudadana transporte público, convivencia en TransMilenio, emociones y comportamiento ciudadano, investigación cultura ciudadana, medición de percepción ciudadana, transformación cultural urbana</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>13</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -981,10 +1144,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Viviana Rodríguez, Laura Lozano, Giovani Moreno, Diego Lemus</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>59</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1047,10 +1232,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Carlos Suárez, Giovani Moreno, Laura Lozano</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>95</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1112,12 +1319,30 @@
           <t>Ecosistema cultural, oferta artística nocturna, 24/7, noche, oferta cultural, economía</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Viviana Rodríguez, Carlos Suárez, Giovani Moreno,  Laura Lozano</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1178,42 +1403,60 @@
           <t>Formación, prácticas, cultura, patrimonio, arte</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Gisela Castrillón, Diego Lemus, Germán Urbina</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>8/10/2025</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Percepción ciudadana sobre el Premio Luis Caballero</t>
+          <t>Caracterización de Entidades Sin Ánimo de Lucro 2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medir la percepción del público visitante sobre el Premio Luis Caballero, valorando conocimientos, emociones y sentido otorgado a las exposiciones, para orientar futuras ediciones y estrategias de mediación.</t>
+          <t>Segunda etapa del estudio sectorial iniciado en 2024, enfocado en actualizar y profundizar la caracterización de las Entidades Sin Ánimo de Lucro (ESAL) adscritas a la SCRD, abordando aspectos de infraestructura, oferta de valor, sostenibilidad financiera y modelos de gestión.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IDARTES</t>
+          <t>SCRD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>202591004200100009E</t>
+          <t>202591004200100004E</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IDARTES G Plásticas</t>
+          <t>Gobernanza - DPJ</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1229,31 +1472,65 @@
           <t>Sector Cultura</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Realizar un análisis de la información recolectada en los formularios aplicados a las ESALES 2024 y 2025, en términos de oferta de valor, estructura organizacional y herramientas de sostenibilidad.
+</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1qEkfdB8IzvAAAQS-Q6Dbmi1B1iui7bhP</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+          <t>https://drive.google.com/drive/folders/1GPyUMdbxqqJ-fja7DNFswVLKyoucNKao</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Dirección de Personas Juridicas, ESALES Culturales, Oferta de Valor, Infraestructura, Sostenibilidad, economía</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giovani Moreno,Carlos Suárez </t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>58</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caracterización del sector circo – Fase 2</t>
+          <t>Percepción ciudadana sobre el Premio Luis Caballero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segunda fase del diagnóstico del sector circense en Bogotá, que ampliará el inventario georreferenciado de agentes y espacios, e incluirá un análisis de las condiciones técnicas, económicas y de oferta para fortalecer estrategias de apoyo al sector.
-</t>
+          <t>Medir la percepción del público visitante sobre el Premio Luis Caballero, valorando conocimientos, emociones y sentido otorgado a las exposiciones, para orientar futuras ediciones y estrategias de mediación.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1263,12 +1540,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>202591004200100010E</t>
+          <t>202591004200100009E</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IDARTES G Dramático</t>
+          <t>IDARTES G Plásticas</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1284,27 +1561,37 @@
           <t>Sector Cultura</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Profundizar en el conocimiento de las características, necesidades y distribución territorial del sector circense en Bogotá, con el fin de fortalecer los lineamientos para la formulación de políticas públicas y programas que respondan de manera pertinente a su realidad e incidencia en las localidades de la ciudad.</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1hf4-sbaDvKEyxKOBEDUutNLalZjrUZbp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Circo - Prácticas circenses - georreferenciación - Caracterización espacios y actores</t>
-        </is>
-      </c>
+          <t>https://drive.google.com/drive/folders/1qEkfdB8IzvAAAQS-Q6Dbmi1B1iui7bhP</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viviana Rodríguez, Carlos Suárez </t>
-        </is>
-      </c>
-      <c r="N14" t="n">
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>22</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1368,40 +1655,63 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>VivianaRodríguez, Laura Lozano, Giovani Moreno, Diego Lemus</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
+        <v>9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>331</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Percepciones sobre el Festival Centro 2025</t>
+          <t>Caracterización del sector circo – Fase 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Análisis de las percepciones de asistentes y actores vinculados al Festival Centro 2025, con base en la información ya recolectada, para identificar oportunidades de mejora y fortalecer futuras ediciones.</t>
+          <t xml:space="preserve">Segunda fase del diagnóstico del sector circense en Bogotá, que ampliará el inventario georreferenciado de agentes y espacios, e incluirá un análisis de las condiciones técnicas, económicas y de oferta para fortalecer estrategias de apoyo al sector.
+</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUGA</t>
+          <t>IDARTES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>202591004200100012E</t>
+          <t>202591004200100010E</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FUGA - Artística</t>
+          <t>IDARTES G Dramático</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1419,21 +1729,47 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Realizar el análisis de resultados de la medición del Festival Centro 2025, centrada en la aplicaicón del instrumento orientado a asistentes</t>
+          <t>Profundizar en el conocimiento de las características, necesidades y distribución territorial del sector circense en Bogotá, con el fin de fortalecer los lineamientos para la formulación de políticas públicas y programas que respondan de manera pertinente a su realidad e incidencia en las localidades de la ciudad.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1btfJ10uYqzIsb9OBp_9cS1u-KQ_WPMr8</t>
+          <t>https://drive.google.com/drive/folders/1hf4-sbaDvKEyxKOBEDUutNLalZjrUZbp</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Festival - Música - Centro - Asistentes</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+          <t>Circo - Prácticas circenses - georreferenciación - Caracterización espacios y actores</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viviana Rodríguez, Carlos Suárez </t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>46</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1496,10 +1832,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Laura Lozano - Giovani Moreno</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>152</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1514,7 +1872,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">La investigación analiza el uso, la apropiación y el aprovechamiento de cinco parques estructurantes de Bogotá a partir de información recolectada mediante encuestas presenciales a personas usuarias. El estudio caracteriza los perfiles de uso, los horarios, las actividades realizadas, con énfasis en la práctica de actividad física, y las formas de acompañamiento, así como las percepciones sobre el estado físico, el mantenimiento y la seguridad de los espacios. Los resultados identifican barreras y oportunidades para fortalecer el uso de los parques y evidencian una brecha entre el interés declarado y la participación efectiva en actividades culturales y recreativas.
+          <t xml:space="preserve">Análisis del uso, la apropiación y el aprovechamiento de cinco parques estructurantes de Bogotá a partir de información recolectada mediante encuestas presenciales a personas usuarias. El estudio caracteriza los perfiles de uso, los horarios, las actividades realizadas, con énfasis en la práctica de actividad física, y las formas de acompañamiento, así como las percepciones sobre el estado físico, el mantenimiento y la seguridad de los espacios. Los resultados identifican barreras y oportunidades para fortalecer el uso de los parques y evidencian una brecha entre el interés declarado y la participación efectiva en actividades culturales y recreativas.
 </t>
         </is>
       </c>
@@ -1555,10 +1913,32 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>Julian Chavez,Laura Lozano</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1617,10 +1997,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>Julian Chavez,Laura Lozano</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1679,40 +2081,62 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>Andrea García,Laura Lozano</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medición de eventos culturales de gran formato del IDPC</t>
+          <t>Percepciones sobre el Festival Centro 2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>La investigación se orienta a la caracterización de públicos y al análisis de percepciones asociadas a los eventos culturales de gran formato del IDPC, con el fin de evaluar los impactos culturales, sociales y económicos de la Noche de Museos, la Noche Iberoamericana de Museos y el Festival de Patrimonios en Ruana. El estudio analiza la composición y perfiles de asistencia, los niveles de satisfacción, los patrones de consumo, la percepción de marca y los aportes de los festivales al posicionamiento de Bogotá como ciudad de grandes eventos. Los resultados constituyen insumos estratégicos para la toma de decisiones, el fortalecimiento de la oferta cultural y la proyección de la ciudad a nivel nacional e internacional.</t>
+          <t>Análisis de las percepciones de asistentes y actores vinculados al Festival Centro 2025, con base en la información ya recolectada, para identificar oportunidades de mejora y fortalecer futuras ediciones.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IDPC</t>
+          <t>FUGA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>202591004200100013E</t>
+          <t>202591004200100012E</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IDPC Divulgación</t>
+          <t>FUGA - Artística</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1730,55 +2154,73 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Realizar el diseño metodologico y aplicación de las mediciones tres eventos organizados por el IDPC (noche de museos, noche Iberoamercana de Museos y Festival de Patrimonios en Ruana)</t>
+          <t>Realizar el análisis de resultados de la medición del Festival Centro 2025, centrada en la aplicaicón del instrumento orientado a asistentes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1xjocKAYz8q0DO-L6hTN_wWcd077f-n3V</t>
+          <t>https://drive.google.com/drive/folders/1btfJ10uYqzIsb9OBp_9cS1u-KQ_WPMr8</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Noches de Museos, IDPC, Museos, Patrimonio Cultural, Bogotá nocturna.</t>
+          <t>Festival - Música - Centro - Asistentes</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Giovani Moreno ,todo el equipo</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>42</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PENDIENTE REEMPLAZA AGENTES</t>
+          <t>Medición de eventos culturales de gran formato del IDPC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Caracterización de la asociatividad y sostenibilidad de agentes del sector. No se llegó a difinir la investigaicón que reemplazaría. Se marca como cancelda.</t>
+          <t>La investigación se orienta a la caracterización de públicos y al análisis de percepciones asociadas a los eventos culturales de gran formato del IDPC, con el fin de evaluar los impactos culturales, sociales y económicos de la Noche de Museos, la Noche Iberoamericana de Museos y el Festival de Patrimonios en Ruana. El estudio analiza la composición y perfiles de asistencia, los niveles de satisfacción, los patrones de consumo, la percepción de marca y los aportes de los festivales al posicionamiento de Bogotá como ciudad de grandes eventos. Los resultados constituyen insumos estratégicos para la toma de decisiones, el fortalecimiento de la oferta cultural y la proyección de la ciudad a nivel nacional e internacional.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SCRD</t>
+          <t>IDPC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>202591004200100014E</t>
+          <t>202591004200100013E</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gobernanza - Fomento</t>
+          <t>IDPC Divulgación</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1786,124 +2228,160 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9 Cancelada</t>
+          <t>5 Finalizada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cultura Ciudadana</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Sector Cultura</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Realizar el diseño metodologico y aplicación de las mediciones tres eventos organizados por el IDPC (noche de museos, noche Iberoamercana de Museos y Festival de Patrimonios en Ruana)</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1S-Bf8soIeS71sk3a5vco8X45vVaUNM3l</t>
+          <t>https://drive.google.com/drive/folders/1xjocKAYz8q0DO-L6hTN_wWcd077f-n3V</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asociatividad agentes, Fomento, </t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
+          <t>Noches de Museos, IDPC, Museos, Patrimonio Cultural, Bogotá nocturna.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Giovani Moreno ,todo el equipo</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>45</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>111</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PENDIENTE REEMPLAZA AGENTES</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Caracterización de la asociatividad y sostenibilidad de agentes del sector. No se llegó a difinir la investigaicón que reemplazaría. Se marca como cancelda.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SCRD</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>202591004200100014E</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gobernanza - Fomento</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>9 Cancelada</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Cultura Ciudadana</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1S-Bf8soIeS71sk3a5vco8X45vVaUNM3l</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asociatividad agentes, Fomento, </t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>112</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Teatro de creación colectiva</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t xml:space="preserve">Continuación del proceso de identificación y caracterización de grupos y espacios vinculados al teatro de creación colectiva en localidades de Bogotá, con priorización territorial y fases sucesivas de aplicación y sistematización.
 </t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>IDPC</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>202591004200100015E</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>IDPC Divulgación</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>5 Finalizada</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sector Cultura</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Avanzar en la ejecución de las fases 2 y 3 del proyecto, mediante el levantamiento, sistematización y análisis de información sobre grupos, colectivos, organizaciones y espacios en las distintas localidades de la ciudad, con el fin de fortalecer el directorio de actores, aplicar instrumentos de caracterización en territorios priorizados y divulgar los resultados en el marco del Colectivo de la Salvaguardia.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/13jmKoZRuSXFpQfQpwt5x18N_T5o5Quzs</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Creación colectiva - Teatro - Agrupaciones teatrales</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Viviana Rodríguez</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>113</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>EBC - Encuesta de Lectura, Escritura y Oralidad 2025</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Diseño, aplicación y análisis del módulo de Lectura, Escritura y Oralidad en la Encuesta Bienal de Culturas 2025, en articulación con la Dirección de Lectura y Bibliotecas. Incluye trabajo de campo por muestreo probabilístico, procesamiento de datos y análisis de resultados.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>SCRD</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>202591004200100016E</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SCCGC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1921,25 +2399,43 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Obtener información que permita hacer seguimiento a la política pública LEO y caracterizar los hábitos de lectura, escritura y oralidad. Recoge los conocimientos, actitudes, valoraciones, emociones y percepciones frente a la lectura, la escritura y la oralidad.</t>
+          <t>Avanzar en la ejecución de las fases 2 y 3 del proyecto, mediante el levantamiento, sistematización y análisis de información sobre grupos, colectivos, organizaciones y espacios en las distintas localidades de la ciudad, con el fin de fortalecer el directorio de actores, aplicar instrumentos de caracterización en territorios priorizados y divulgar los resultados en el marco del Colectivo de la Salvaguardia.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1sTNCho5MGwcW5BVNJa4KYzMzVgdYCLeG</t>
+          <t>https://drive.google.com/drive/folders/13jmKoZRuSXFpQfQpwt5x18N_T5o5Quzs</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>lectura, bibliotecas, oralidad, podcast, libros, escritura, espacios de lectura, virgilio barco, bibliored</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Viviana Rodríguez, Carlos Suárez, Giovani Moreno, Laura Lozano</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
+          <t>Creación colectiva - Teatro - Agrupaciones teatrales</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Viviana Rodríguez</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>60</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1996,12 +2492,30 @@
           <t>barrios vivos, territorial, sistemas de información, cronograma, actividades, descripción, seguimiento, monitoreo</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>Mauricio Ojeda, Mábel Ayala</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>16/10/25</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2060,10 +2574,32 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>Viviana Rodríguez, Carlos Suárez, Giovani Moreno, Laura Lozano</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2127,10 +2663,32 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>Giovani Moreno ,todo el equipo</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2185,10 +2743,32 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
+          <t>SinProductos</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>Carlos Suárez,Todo el equipo</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2241,12 +2821,30 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Daniel Galeano</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2303,12 +2901,30 @@
           <t>género enfoque espacio público centro de bogotá</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Daniel Galeano</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2367,10 +2983,32 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>PocosProductos</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>Jhonatan Rosas</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2425,10 +3063,32 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
+          <t>PocosProductos</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Jhonatan Rosas</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2481,12 +3141,30 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>Daniel Galeano</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>49</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2539,12 +3217,30 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Viviana Rodriguez</t>
         </is>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>22</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>23/11/2025</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2559,7 +3255,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Diseño y recolección de la Encuesta de Indicadores de Cultura Ciudadana y Garantía de Derechos 2025, como módulo de la Encuesta Bienal de Culturas</t>
+          <t>Encuesta de Indicadores de Cultura Ciudadana y Garantía de Derechos 2025, como módulo de la Encuesta Bienal de Culturas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2578,7 +3274,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1 Sin iniciar</t>
+          <t>5 Finalizada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2594,11 +3290,33 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>cultura ciudadana, indicadores, variables, monitoreo, seguimiento, política, ambiente, participación, género, política</t>
+          <t>cultura ciudadana, indicadores, variables, monitoreo, seguimiento, política, ambiente, participación, género, política, creencias, machismo, maternidad, inclusión, descriminación, localidades, paz, convivencia, confianza</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Melina Moncada, Daniel Galeano, Jhonatan Rosas</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2651,12 +3369,30 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>Jhonatan Rosas</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2714,7 +3450,25 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2767,12 +3521,30 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>Jhonatan Rosas</t>
         </is>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2818,7 +3590,21 @@
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2860,7 +3646,21 @@
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -2911,10 +3711,32 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
+          <t>Agenda cultural y política, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>Mábel Ayala, Mauricio Ojeda</t>
         </is>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
+        <v>6</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>13/12/2024</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -2975,8 +3797,30 @@
           <t>icc 2023 cultura ciudadana, visualización, power bi, encuesta bienal de culturas, ebc 2023, inclusión, movilidad, género, discriminación, orgullo</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>26/11/24</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3033,8 +3877,26 @@
           <t>movilidad, transmilenio, estaciones orgullo apropiación confianza sentimientos emociones cambio de comportamiento evasión pasajes colados</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3097,10 +3959,32 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>Comunidades creadoras, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>Mábel Ayala Meneses, Mauricio Ojeda Pepinosa</t>
         </is>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
+        <v>6</v>
+      </c>
+      <c r="P44" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>39</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>26/11/2024</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3157,8 +4041,30 @@
           <t>IDARTES, Festivales, Al Parque, Asistentes, Artistas, Emprendedores, Música en vivo, eventos, espectáculos, rock, vallenato, popular, salsa</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="n">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Agenda cultural y política, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>10</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>31/12/2024</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3213,10 +4119,28 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
+          <t>EBC, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>Carlos Suárez, Viviana Rodriguez</t>
         </is>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
+        <v>6</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3279,10 +4203,32 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>Susana Restrepo, Mauricio Ojeda Pepinosa</t>
         </is>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
+        <v>7</v>
+      </c>
+      <c r="P47" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>28/11/2024</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3343,8 +4289,30 @@
           <t>OFB, Música, Formación, Impacto, NNAJ (niños, niñas, adolescentes y jóvenes)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>2</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>19/12/2024</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3407,10 +4375,32 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>Viviana Rodriguez, Susana Restrepo</t>
         </is>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
+        <v>4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>30/12/2024</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3469,10 +4459,28 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>Viviana Rodriguez y Carlos Suarez</t>
         </is>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
+        <v>8</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3530,7 +4538,25 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="n">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>23/12/2024</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3588,7 +4614,25 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>6</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>28/11/2024</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3651,10 +4695,32 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>Susana Restrepo/ Viviana Rodríguez/</t>
         </is>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>27/12/2024</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3708,7 +4774,25 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>28/11/2024</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3762,7 +4846,25 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>3</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>04/12/2024</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3821,7 +4923,25 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>6</v>
+      </c>
+      <c r="P56" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>5</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>27/12/2024</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3878,8 +4998,26 @@
           <t>Comportamientos ambientales, protección animal, biodoversidad, cuidado del agua, infraestructura ecológica, ebc, encuesta bienal de culturas</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>EBC</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -3942,10 +5080,32 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
           <t>Viviana Rodriguez / Gisela Castrillon</t>
         </is>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>27/12/2024</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4008,10 +5168,32 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
           <t>Susana Restrepo/ Viviana Rodríguez/</t>
         </is>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
+        <v>5</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>5</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>26/12/2024</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4074,10 +5256,32 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
           <t>Susana Restrepo / Carlos David Suarez</t>
         </is>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
+        <v>2</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>27/12/2024</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4135,7 +5339,25 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>29/11/24</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4193,7 +5415,25 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>29/11/24</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4251,7 +5491,21 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4305,7 +5559,25 @@
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="n">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>18/12/24</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4359,7 +5631,25 @@
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>30/12/24</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4417,7 +5707,25 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>5</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>7</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4476,7 +5784,25 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>21/10/2024</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4533,12 +5859,30 @@
           <t>deep, 24 horas, economía cultural, consumo cultural, bogotá 24 horas, nocturno, noche, rumba</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
+        <v>3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>26/12/2024</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4596,7 +5940,25 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>19/11/2024</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4654,7 +6016,25 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>3</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>5</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>30/12/2024</t>
+        </is>
+      </c>
+      <c r="T70" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4704,7 +6084,21 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4753,7 +6147,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>90 Seguridad y riñas</t>
+          <t>https://drive.google.com/drive/folders/1nOZZDp39DWeQQDpFuIlxkQBlgR216qwD?usp=drive_link</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4762,7 +6156,25 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>5</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>29/12/2024</t>
+        </is>
+      </c>
+      <c r="T72" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4821,10 +6233,32 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Viviana Rodriguez </t>
         </is>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
+        <v>2</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>18/12/2024</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4866,7 +6300,21 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="n">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4908,7 +6356,21 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -4950,7 +6412,21 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -5002,7 +6478,21 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="n">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -5050,7 +6540,21 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -5094,7 +6598,21 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="n">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -5153,10 +6671,28 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
+          <t>Acción colectiva, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Carlos David Suárez Morales, Alexandra Moreno Arteaga,Karen Julieth Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N80" t="n">
+      <c r="O80" t="n">
+        <v>9</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>4</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5219,10 +6755,32 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
+          <t>Libertad e identidad, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Daniel Galeano Amaya, Mábel Ayala Meneses, Mauricio Ojeda Pepinosa, Sandra Milena Murcia</t>
         </is>
       </c>
-      <c r="N81" t="n">
+      <c r="O81" t="n">
+        <v>4</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>23/10/2023</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5285,10 +6843,32 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Alexandra Moreno Arteaga, Jorge Mario Guerrero Bedoya, Karen Julieth Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N82" t="n">
+      <c r="O82" t="n">
+        <v>3</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4</v>
+      </c>
+      <c r="R82" t="n">
+        <v>27</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>28/12/2023</t>
+        </is>
+      </c>
+      <c r="T82" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5352,10 +6932,32 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
+          <t>Diversidad y diálogo intercultural</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>Karen Vanessa Marriner, Karen Julieth Higuera Rodríguez, Mabel Ayala y Gisela Gastrillón, Rafael Villa, Marcela Garzón</t>
         </is>
       </c>
-      <c r="N83" t="n">
+      <c r="O83" t="n">
+        <v>7</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>4</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>27/12/2023</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5420,10 +7022,32 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Viviana Marcela Rodríguez, Karen Julieth Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N84" t="n">
+      <c r="O84" t="n">
+        <v>7</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>5</v>
+      </c>
+      <c r="R84" t="n">
+        <v>26</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>7/9/2023</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5486,11 +7110,33 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
+          <t>Acción colectiva</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Viviana Marcela Rodríguez
 Amaya, Karen Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N85" t="n">
+      <c r="O85" t="n">
+        <v>6</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>5</v>
+      </c>
+      <c r="R85" t="n">
+        <v>34</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>26/10/2023</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5553,10 +7199,32 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Carlos David Suárez, Daniela Camacho Bernal, Karen Julieth Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N86" t="n">
+      <c r="O86" t="n">
+        <v>5</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>4</v>
+      </c>
+      <c r="R86" t="n">
+        <v>47</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>04/10/2023</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5615,10 +7283,32 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Alexandra Moreno Arteaga, Gustavo Romero Cruz, Andrés José León Palencia, Juan Diego Jaramillo Morales</t>
         </is>
       </c>
-      <c r="N87" t="n">
+      <c r="O87" t="n">
+        <v>6</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>25</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>29/09/2023</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5681,11 +7371,33 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Viviana Marcela Rodríguez, Karen Julieth Higuera
 Rodríguez</t>
         </is>
       </c>
-      <c r="N88" t="n">
+      <c r="O88" t="n">
+        <v>3</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5</v>
+      </c>
+      <c r="R88" t="n">
+        <v>75</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>18/10/2023</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5748,10 +7460,32 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
+          <t>Acción colectiva</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
           <t>Carlos David Suarez Morales, Diego Caicedo, Marcela Garzón García, Karen Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N89" t="n">
+      <c r="O89" t="n">
+        <v>5</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>5</v>
+      </c>
+      <c r="R89" t="n">
+        <v>97</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>18/10/2023</t>
+        </is>
+      </c>
+      <c r="T89" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5814,10 +7548,28 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
+          <t>Comunidades creadoras, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Karen Higuera Rodríguez, Gisela Castrillón Moreno, Sandra Milena Murcia</t>
         </is>
       </c>
-      <c r="N90" t="n">
+      <c r="O90" t="n">
+        <v>3</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>2</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5880,10 +7632,32 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Alexandra Moreno Arteaga, Karen Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N91" t="n">
+      <c r="O91" t="n">
+        <v>5</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>4</v>
+      </c>
+      <c r="R91" t="n">
+        <v>39</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>28/12/2023</t>
+        </is>
+      </c>
+      <c r="T91" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -5940,8 +7714,30 @@
           <t>música en vivo, festival al parque, espectáculos, idartes, eventos, emprendimiento, rock, economía, parque simón bolívar, consumo cultural, festivales</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="n">
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Libertad e identidad</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>6</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>4</v>
+      </c>
+      <c r="R92" t="n">
+        <v>35</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>27/12/2023</t>
+        </is>
+      </c>
+      <c r="T92" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6000,10 +7796,32 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
+          <t>Libertad e identidad</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Carlos David Suárez Morales, Karen Julieth Higuera Rodríguez, Daniela Camacho Bernal, Karen Julieth Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N93" t="n">
+      <c r="O93" t="n">
+        <v>6</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>5</v>
+      </c>
+      <c r="R93" t="n">
+        <v>37</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>11/07/2023</t>
+        </is>
+      </c>
+      <c r="T93" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6066,10 +7884,32 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
+          <t>Comunidades creadoras</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Carlos David Suárez M, Alexandra Moreno Arteaga, Karen Julieth Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N94" t="n">
+      <c r="O94" t="n">
+        <v>9</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>4</v>
+      </c>
+      <c r="R94" t="n">
+        <v>43</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>02/11/2023</t>
+        </is>
+      </c>
+      <c r="T94" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6132,10 +7972,32 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
+          <t>Acción colectiva, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Viviana Rodríguez Amaya, Gisela Castrillón Moreno, Karen Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N95" t="n">
+      <c r="O95" t="n">
+        <v>6</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>4</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>20/12/2023</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6198,10 +8060,32 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Libertad e identidad</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Carlos David Suárez M, Alexandra Moreno Arteaga, Karen Julieth Higuera Rodríguez</t>
         </is>
       </c>
-      <c r="N96" t="n">
+      <c r="O96" t="n">
+        <v>8</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5</v>
+      </c>
+      <c r="R96" t="n">
+        <v>50</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>02/11/2023</t>
+        </is>
+      </c>
+      <c r="T96" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6260,10 +8144,32 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
+          <t>Libertad e identidad</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
           <t>Marcela Garzón García,Carlos David Suárez Morales,Karen Julieth Higuera Rodríguez,Alexandra Moreno Arteaga</t>
         </is>
       </c>
-      <c r="N97" t="n">
+      <c r="O97" t="n">
+        <v>6</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>3</v>
+      </c>
+      <c r="R97" t="n">
+        <v>41</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>11/07/2023</t>
+        </is>
+      </c>
+      <c r="T97" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6322,12 +8228,34 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
+          <t>Libertad e identidad</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Viviana Marcela
 Rodríguez, Karen Julieth Higuera
 Rodríguez</t>
         </is>
       </c>
-      <c r="N98" t="n">
+      <c r="O98" t="n">
+        <v>5</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>5</v>
+      </c>
+      <c r="R98" t="n">
+        <v>16</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>22/08/2023</t>
+        </is>
+      </c>
+      <c r="T98" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6388,8 +8316,26 @@
           <t>redes sociales twitter x social listening, cultura digital, discriminación pai 2024, cultura ciudadana, etnias, lgbti, venezolanos, migrantes, indígenas, afro, narp, racismo, clasismo, narrativas, insultos, derechos</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="n">
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Diversidad y diálogo intercultural, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>2</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>5</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6452,10 +8398,28 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
+          <t>Acción colectiva, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
           <t>Karen Marriner, Francisco Franco, Daniel Galeano Amaya</t>
         </is>
       </c>
-      <c r="N100" t="n">
+      <c r="O100" t="n">
+        <v>2</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>4</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6512,8 +8476,26 @@
           <t>Género, Escuela Hombres al cuidado, Cuidado, Cultura ciudadana, Hogar, Casa, Hombres</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="n">
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="n">
+        <v>2</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>5</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6566,8 +8548,26 @@
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="n">
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Libertad e identidad, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="n">
+        <v>2</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>3</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6626,10 +8626,28 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
           <t>Andrea Katherine Daza, Rafael Hurtado, Carlos David Suarez, Paula Larotta Cedano, Rafael Ricardo Villa Rojas</t>
         </is>
       </c>
-      <c r="N103" t="n">
+      <c r="O103" t="n">
+        <v>4</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>5</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6688,10 +8706,28 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
           <t>Sandra Milena Murcia, Juan Pablo Hortúa, Jasson Iván Pinillos Hincapié</t>
         </is>
       </c>
-      <c r="N104" t="n">
+      <c r="O104" t="n">
+        <v>9</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>5</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6754,10 +8790,28 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>Daniel Galeano Amaya, Paula González Vergara, Karen Marriner Castro, Rafael Villa Rojas, Isabel Betancourt Argüelles, Juan Diego Jaramillo</t>
         </is>
       </c>
-      <c r="N105" t="n">
+      <c r="O105" t="n">
+        <v>3</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>5</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6816,10 +8870,28 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
+          <t>Libertad e identidad, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
           <t>Mábel Ayala Meneses, Marcela Garzón García, Camilo Tiria Buitrago, Mauricio Ojeda Pepinosa</t>
         </is>
       </c>
-      <c r="N106" t="n">
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6878,10 +8950,26 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
+          <t>Diversidad y diálogo intercultural, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
           <t>Viviana Marcela Rodríguez, Amaya, Marcela Garzón García</t>
         </is>
       </c>
-      <c r="N107" t="n">
+      <c r="O107" t="n">
+        <v>8</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6931,8 +9019,24 @@
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="n">
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="n">
+        <v>3</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="n">
+        <v>61</v>
+      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -6995,10 +9099,28 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
+          <t>Acción colectiva, InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
           <t>Paula González Vergara, Karen Marriner, Rafael Ricardo Villa</t>
         </is>
       </c>
-      <c r="N109" t="n">
+      <c r="O109" t="n">
+        <v>2</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7057,10 +9179,28 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
           <t>Rafael Villa Roja, Karen Vanesa Marriner</t>
         </is>
       </c>
-      <c r="N110" t="n">
+      <c r="O110" t="n">
+        <v>3</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>5</v>
+      </c>
+      <c r="R110" t="n">
+        <v>41</v>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7123,10 +9263,28 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
           <t>Paula González Vergara, Paula La Rotta Cedano, Rafael Ricardo Villa Rojas</t>
         </is>
       </c>
-      <c r="N111" t="n">
+      <c r="O111" t="n">
+        <v>2</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>5</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7185,10 +9343,28 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
           <t>Rafael Villa Rojas, Karen Vanesa Marriner, Daniel Galeano Amaya</t>
         </is>
       </c>
-      <c r="N112" t="n">
+      <c r="O112" t="n">
+        <v>4</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>5</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7247,10 +9423,28 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
+          <t>InventarioBogota</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
           <t>Daniel Galeano Amaya, Karen Marriner-Castro, Rafael Ricardo Villa Rojas</t>
         </is>
       </c>
-      <c r="N113" t="n">
+      <c r="O113" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>5</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7313,10 +9507,28 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
           <t>Mauricio Ojeda Pepinosa</t>
         </is>
       </c>
-      <c r="N114" t="n">
+      <c r="O114" t="n">
+        <v>4</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>5</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7369,8 +9581,30 @@
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="n">
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Acción colectiva</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="n">
+        <v>7</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>30/11/2023</t>
+        </is>
+      </c>
+      <c r="T115" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7429,10 +9663,32 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
           <t>Dayana Alexandra Moreno Arteaga, Karen Julieth Higuera Rodríguez, Marcela Garzón García</t>
         </is>
       </c>
-      <c r="N116" t="n">
+      <c r="O116" t="n">
+        <v>5</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>4</v>
+      </c>
+      <c r="R116" t="n">
+        <v>20</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>28/12/2023</t>
+        </is>
+      </c>
+      <c r="T116" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7489,8 +9745,30 @@
           <t>música en vivo, festival al parque, espectáculos, idartes, eventos, emprendimiento, festivales</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="n">
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Libertad e identidad</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="n">
+        <v>6</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>2</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>27/12/2023</t>
+        </is>
+      </c>
+      <c r="T117" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7547,8 +9825,26 @@
           <t>ebc 2023 lectura, escritura, oralidad, leo</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="n">
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="n">
+        <v>3</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7605,8 +9901,30 @@
           <t>ebc 2023, encuesta bienal de culturas, consumo cultural, patrimoios, internet, acceso, plan de cultura, equipamientos</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="n">
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Agenda cultural y política</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="n">
+        <v>3</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>6/11/2024</t>
+        </is>
+      </c>
+      <c r="T119" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7667,8 +9985,30 @@
           <t>centro histórico gastrobares restaurantes comida gastronomía sabor bogotá</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="n">
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Acción colectiva</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="n">
+        <v>5</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>5</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>27/12/2023</t>
+        </is>
+      </c>
+      <c r="T120" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7718,7 +10058,21 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="n">
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7781,10 +10135,28 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
+          <t>Libertad e identidad</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
           <t>Mauricio Ojeda Pepinosa, Maritza Téllez</t>
         </is>
       </c>
-      <c r="N122" t="n">
+      <c r="O122" t="n">
+        <v>3</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>5</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7847,10 +10219,28 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
+          <t>Acción colectiva</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
           <t>Mauricio Ojeda Pepinosa</t>
         </is>
       </c>
-      <c r="N123" t="n">
+      <c r="O123" t="n">
+        <v>4</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>5</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7900,7 +10290,21 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="n">
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -7959,10 +10363,28 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
+          <t>Acción colectiva</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
           <t>Karen Marriner, Rafael Villa</t>
         </is>
       </c>
-      <c r="N125" t="n">
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8019,12 +10441,26 @@
           <t>transmilenio, cultura ciudadana, combo violenta, floorgraphics, evasión de pasajes, colados, las aguas, museo del oro, avenida jiménez</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
         <is>
           <t>Paula González Vergara, María del Pilar Acosta Niño, Gisela Castrillón Moreno, Rafael Ricardo Villa Rojas</t>
         </is>
       </c>
-      <c r="N126" t="n">
+      <c r="O126" t="n">
+        <v>3</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>5</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8073,8 +10509,26 @@
           <t>ebc, encuesta bienal de culturas, encuesta de indicadores, cultura ciudadana, encuesta probabilística</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="n">
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Diversidad y diálogo intercultural</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8124,7 +10578,21 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="n">
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8174,7 +10642,21 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="n">
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8224,7 +10706,21 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="n">
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>4</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8281,13 +10777,27 @@
           <t>celos, masculinidades, machismo, línea calma, amor romántico, psicoeducativo, control emocional, comunicación</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
         <is>
           <t>Rafael Villa
 Daniel Galeano</t>
         </is>
       </c>
-      <c r="N131" t="n">
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8350,10 +10860,28 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
+          <t>Diversidad y diálogo intercultural</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
           <t>Mauricio Ojeda Pepinosa</t>
         </is>
       </c>
-      <c r="N132" t="n">
+      <c r="O132" t="n">
+        <v>4</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>5</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8399,7 +10927,21 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="n">
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8458,11 +11000,33 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
+          <t>Acción colectiva</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
           <t>Marcela Garzón García, Viviana Marcela Rodríguez, Karen Julieth Higuera
 Rodríguez, Gisela Castrillón, Gustavo Romero</t>
         </is>
       </c>
-      <c r="N134" t="n">
+      <c r="O134" t="n">
+        <v>7</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>5</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>19/10/2023</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8516,7 +11080,21 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="n">
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8554,7 +11132,19 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="n">
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8600,7 +11190,19 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="n">
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="n">
         <v>2023</v>
       </c>
     </row>
@@ -8615,7 +11217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E732"/>
+  <dimension ref="A1:E737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20082,7 +22684,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>https://lookerstudio.google.com/u/0/reporting/4a928fd5-3d5a-4de3-a655-943ad2da4e6e/page/p_d6cfr52jwd</t>
+          <t>https://datastudio.google.com/u/0/reporting/4a928fd5-3d5a-4de3-a655-943ad2da4e6e/page/eEYFF</t>
         </is>
       </c>
     </row>
@@ -21106,7 +23708,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ysvsCPGJOfu0iRaVnhZLyxQlDeI4MJ2_/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1PnmpSnkkyh4bJVzxfL-RkYnrgoOycMXn/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21131,7 +23733,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1zFYtNPqms3OkOZw6b-waNURvYySD2r8E/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1uvPcjC3VFFwdTN4LKTZqQa4dd_mt6aRq/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21711,12 +24313,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Formulario Final EBC LEO</t>
+          <t>Presentación Resultados</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -21726,7 +24328,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16W6G5tRSMAk7F6SDasy_0yM92zpbwTbq/view?usp=drive_link</t>
+          <t>https://docs.google.com/presentation/d/1yWaRc9exf_bTRLogY91xFm07vA1z9KIVUtMvRjmZROU/edit?slide=id.g39d9e6d9131_0_0#slide=id.g39d9e6d9131_0_0</t>
         </is>
       </c>
     </row>
@@ -21782,7 +24384,7 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -21791,7 +24393,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Espacios de Lectura</t>
+          <t>Formulario Final EBC LEO</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -21801,7 +24403,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16W6G5tRSMAk7F6SDasy_0yM92zpbwTbq/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1yyt1S-79rnJrntKimXHfNVwC1iuCEgBW/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21811,12 +24413,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Usaquén - Servitá</t>
+          <t>Instrumento de recolección Espacios de Lectura</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -21826,7 +24428,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FRWQBJGGoZZttLVMLwagnXXYShR2lFqi/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/16W6G5tRSMAk7F6SDasy_0yM92zpbwTbq/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21841,7 +24443,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública La Peña</t>
+          <t>Sondeo Visitantes Biblioteca Pública Usaquén - Servitá</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -21851,7 +24453,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RwsGRlcn7XYuXJ1rtmYJUnWj69aEpyMV/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1FRWQBJGGoZZttLVMLwagnXXYShR2lFqi/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21866,7 +24468,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública FUGA</t>
+          <t>Sondeo Visitantes Biblioteca Pública La Peña</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -21876,7 +24478,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DYP4zsQhzkx8PH-yydqgAloHd_DCEsTV/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1RwsGRlcn7XYuXJ1rtmYJUnWj69aEpyMV/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21891,7 +24493,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Virgilio Barco</t>
+          <t>Sondeo Visitantes Biblioteca Pública FUGA</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -21901,7 +24503,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1caNM182qy71k48IqO5Mzv168P1KIbDs-/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1DYP4zsQhzkx8PH-yydqgAloHd_DCEsTV/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21916,7 +24518,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Caros E. Restrepo</t>
+          <t>Sondeo Visitantes Biblioteca Pública Virgilio Barco</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -21926,7 +24528,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19dgvioy6RYxY0oUSvS7HrWGkCn6Bdcve/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1caNM182qy71k48IqO5Mzv168P1KIbDs-/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21941,7 +24543,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Francisco José de Caldas</t>
+          <t>Sondeo Visitantes Biblioteca Pública Caros E. Restrepo</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -21951,7 +24553,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Xdo-9N2TnWtBpoKVhiMIb3Cwj2SYmDWR/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/19dgvioy6RYxY0oUSvS7HrWGkCn6Bdcve/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21966,7 +24568,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Gabriel García Márquez - El Tunal</t>
+          <t>Sondeo Visitantes Biblioteca Pública Francisco José de Caldas</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -21976,7 +24578,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-_wpdpR7e4SMEdEdCVZQNFsVSxxFf7Yn/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1Xdo-9N2TnWtBpoKVhiMIb3Cwj2SYmDWR/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -21991,7 +24593,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Julio Mario Santodomingo</t>
+          <t>Sondeo Visitantes Biblioteca Pública Gabriel García Márquez - El Tunal</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -22001,7 +24603,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19-EGROjB7Se6H5BC7lQ-5kcioDv17Aj8/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1-_wpdpR7e4SMEdEdCVZQNFsVSxxFf7Yn/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22016,7 +24618,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Sondeo Visitantes Biblioteca Pública Manuel Zapata Olivella - El Tintal</t>
+          <t>Sondeo Visitantes Biblioteca Pública Julio Mario Santodomingo</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -22026,7 +24628,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1smpXVkZNK0D0NVvXTpaToUpQYbnUsJ2X/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/19-EGROjB7Se6H5BC7lQ-5kcioDv17Aj8/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22034,48 +24636,48 @@
       <c r="A647" t="n">
         <v>114</v>
       </c>
-      <c r="B647" t="inlineStr"/>
-      <c r="C647" t="inlineStr"/>
-      <c r="D647" t="inlineStr"/>
-      <c r="E647" t="inlineStr"/>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Informe final</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Sondeo Visitantes Biblioteca Pública Manuel Zapata Olivella - El Tintal</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1smpXVkZNK0D0NVvXTpaToUpQYbnUsJ2X/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B648" t="inlineStr"/>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
         <v>115</v>
       </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>Presentación resultados programas de Espacios de actividad física</t>
-        </is>
-      </c>
+      <c r="B649" t="inlineStr"/>
+      <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E649" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1qlsGIDoE8xuZRs0DD2wbob15tro_VEMX/view?usp=drive_link</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -22083,22 +24685,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Tablas de resultado Espacios de actividad física</t>
+          <t>Presentación resultados programas de Espacios de actividad física</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1PeAnosF7Ne2O-rSJHyJNPYU_8VyKObOM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1qlsGIDoE8xuZRs0DD2wbob15tro_VEMX/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22108,12 +24710,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Base de datos Espacios de actividad física</t>
+          <t>Tablas de resultado Espacios de actividad física</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -22123,7 +24725,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1pkjosapWgOR6hhHYZF-HqbqKBJZlYhtM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://docs.google.com/spreadsheets/d/1PeAnosF7Ne2O-rSJHyJNPYU_8VyKObOM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22133,12 +24735,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Espacios de actividad física</t>
+          <t>Base de datos Espacios de actividad física</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -22148,7 +24750,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1u4nc5ifpincy8njQifsXd-QfzDxYlwR8/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1pkjosapWgOR6hhHYZF-HqbqKBJZlYhtM/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22158,12 +24760,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Informe final Espacios de actividad física</t>
+          <t>Instrumento de recolección Espacios de actividad física</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -22173,13 +24775,13 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VMhbyOIs4ScBC_JIaaLKz8_A-A7G5cOl/view?usp=sharing</t>
+          <t>https://drive.google.com/file/d/1u4nc5ifpincy8njQifsXd-QfzDxYlwR8/view?usp=drive_link</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -22188,7 +24790,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Informe presentación resultados programas de Ciclovía y Escuela de la bici</t>
+          <t>Informe final Espacios de actividad física</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -22198,7 +24800,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ml0N-5tIACWRSjSXde5tKA2Q9Wn_J-9k/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1VMhbyOIs4ScBC_JIaaLKz8_A-A7G5cOl/view?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22208,12 +24810,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Ciclovía 2025</t>
+          <t>Informe presentación resultados programas de Ciclovía y Escuela de la bici</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -22223,7 +24825,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uwG-2pHQMS6-t0GhwSTGLJ3fWap6L6Y6/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1ml0N-5tIACWRSjSXde5tKA2Q9Wn_J-9k/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22238,7 +24840,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Instrumento de recolección Escuela de la Bici</t>
+          <t>Instrumento de recolección Ciclovía 2025</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -22248,7 +24850,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j44f0nt3hcD7HjD-Ya48stCgjyv2gPDm/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1uwG-2pHQMS6-t0GhwSTGLJ3fWap6L6Y6/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22258,12 +24860,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Tabla de resultado Ciclovía 2025</t>
+          <t>Instrumento de recolección Escuela de la Bici</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -22273,7 +24875,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/16ZpRSW0DGRb8JPE9QCzrLu2VyFN2IXTt/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1j44f0nt3hcD7HjD-Ya48stCgjyv2gPDm/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22288,7 +24890,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Tabla de resultado Escuela de la Bici</t>
+          <t>Tabla de resultado Ciclovía 2025</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -22298,7 +24900,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1zQZjjzdyGr9BkltBh0Xu5ntzvtJ1siUK/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://docs.google.com/spreadsheets/d/16ZpRSW0DGRb8JPE9QCzrLu2VyFN2IXTt/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22308,12 +24910,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Carpeta archivos</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Bases de datos depuras Ciclovía y Escuela de la Bici</t>
+          <t>Tabla de resultado Escuela de la Bici</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -22323,22 +24925,22 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1E04LKSNgVLJxshdGwwWy8BQRzbJwMkGs/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1zQZjjzdyGr9BkltBh0Xu5ntzvtJ1siUK/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Docuento metodológico</t>
+          <t>Bases de datos depuras Ciclovía y Escuela de la Bici</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -22348,7 +24950,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aRQvwNu04n8HAXbE9o69GhoBogD2Uqj6/view?usp=sharing</t>
+          <t>https://drive.google.com/file/d/1E04LKSNgVLJxshdGwwWy8BQRzbJwMkGs/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22358,12 +24960,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Instrumento de recolección</t>
+          <t>Docuento metodológico</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -22373,7 +24975,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1VZIqZvzrUOBhPEVGF_n98ZthOb8RmV4V/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1aRQvwNu04n8HAXbE9o69GhoBogD2Uqj6/view?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22383,12 +24985,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Matriz de revisión de literatura</t>
+          <t>Instrumento de recolección</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -22398,7 +25000,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U5vso-3VmBTA0uPp6Jwz3zolvbWR17sT/view?usp=drive_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1VZIqZvzrUOBhPEVGF_n98ZthOb8RmV4V/edit?usp=drive_link&amp;ouid=114639277514087565011&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22413,8 +25015,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matriz de tipología de actores
-</t>
+          <t>Matriz de revisión de literatura</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -22424,7 +25025,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HQUAEOPZWxBtWc-dexksGmXsqH3VLyB3/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1U5vso-3VmBTA0uPp6Jwz3zolvbWR17sT/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22439,7 +25040,8 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Matriz de esquema interpretativo de la gobernanza del deporte</t>
+          <t xml:space="preserve">Matriz de tipología de actores
+</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -22449,7 +25051,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16EFX41hHQvz_pSfEG86A1RV2KQ969hzt/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1HQUAEOPZWxBtWc-dexksGmXsqH3VLyB3/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22459,47 +25061,47 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Anexo</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Matriz de esquema interpretativo de la gobernanza del deporte</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1t70D31QSK9xXUEgVSMhUzuwxOwgYAfyO/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/16EFX41hHQvz_pSfEG86A1RV2KQ969hzt/view?usp=drive_link</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Formulario EBC - PACCP Final</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1qsclq1ogNVWTc6Sh7swGgV-k7DZr-Wnj/edit?usp=drive_link&amp;ouid=105090632649587320414&amp;rtpof=true&amp;sd=true</t>
+          <t>https://drive.google.com/file/d/1t70D31QSK9xXUEgVSMhUzuwxOwgYAfyO/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22509,12 +25111,24 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
-      <c r="E667" t="inlineStr"/>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Formulario EBC - PACCP Final</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1qsclq1ogNVWTc6Sh7swGgV-k7DZr-Wnj/edit?usp=drive_link&amp;ouid=105090632649587320414&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -22522,7 +25136,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -22533,7 +25147,11 @@
       <c r="A669" t="n">
         <v>118</v>
       </c>
-      <c r="B669" t="inlineStr"/>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Informe cuantitativo</t>
+        </is>
+      </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr"/>
@@ -22558,37 +25176,37 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>119</v>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>Carpeta archivos</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>Productos finales Festival de Verano 2025</t>
-        </is>
-      </c>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E672" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/14Ap2CtsPvGqgr55CTIh_z0MO3XnfklKi?usp=sharing</t>
-        </is>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B672" t="inlineStr"/>
+      <c r="C672" t="inlineStr"/>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="n">
         <v>119</v>
       </c>
-      <c r="B673" t="inlineStr"/>
-      <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Carpeta archivos</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Productos finales Festival de Verano 2025</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/14Ap2CtsPvGqgr55CTIh_z0MO3XnfklKi?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -22628,28 +25246,12 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>120</v>
-      </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>Carpeta archivos</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
-        <is>
-          <t>Productos finales Concurso Internacional de Violín 2025</t>
-        </is>
-      </c>
-      <c r="D678" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E678" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/114QuIa8ZzjC_GNjRUVggtFVTN3y_zOAL?usp=sharing</t>
-        </is>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B678" t="inlineStr"/>
+      <c r="C678" t="inlineStr"/>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -22662,7 +25264,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Productos finales Bienal Internacional de Arte y Ciudad BOG25</t>
+          <t>Productos finales Concurso Internacional de Violín 2025</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -22672,7 +25274,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/17Bi6a6nKxYmJNqTEWtIH6lYiXMxIECYi?usp=sharing</t>
+          <t>https://drive.google.com/drive/folders/114QuIa8ZzjC_GNjRUVggtFVTN3y_zOAL?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22687,7 +25289,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Productos finales Navidad es Cultura 2025</t>
+          <t>Productos finales Bienal Internacional de Arte y Ciudad BOG25</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -22697,7 +25299,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1rb7lrObK-r5g1iF6SsaYKbR-J_K7nLy-?usp=sharing</t>
+          <t>https://drive.google.com/drive/folders/17Bi6a6nKxYmJNqTEWtIH6lYiXMxIECYi?usp=sharing</t>
         </is>
       </c>
     </row>
@@ -22705,10 +25307,26 @@
       <c r="A681" t="n">
         <v>120</v>
       </c>
-      <c r="B681" t="inlineStr"/>
-      <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
-      <c r="E681" t="inlineStr"/>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Carpeta archivos</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Productos finales Navidad es Cultura 2025</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1rb7lrObK-r5g1iF6SsaYKbR-J_K7nLy-?usp=sharing</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -22730,28 +25348,12 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>121</v>
-      </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>Visualización</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>Tablero Encuesta</t>
-        </is>
-      </c>
-      <c r="D684" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>https://lookerstudio.google.com/reporting/ccbecff5-f250-4a21-b1f8-5290632c1187/page/p_shhgwuepsd</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B684" t="inlineStr"/>
+      <c r="C684" t="inlineStr"/>
+      <c r="D684" t="inlineStr"/>
+      <c r="E684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -22759,12 +25361,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Instrucciones sobre registro de información</t>
+          <t>Tablero Encuesta</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -22774,7 +25376,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gbIyrWH8cK07q00yoPBs9D8IWYNv4P2I/view?usp=drive_link</t>
+          <t>https://lookerstudio.google.com/reporting/ccbecff5-f250-4a21-b1f8-5290632c1187/page/p_shhgwuepsd</t>
         </is>
       </c>
     </row>
@@ -22784,12 +25386,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Prototipo para registro</t>
+          <t>Instrucciones sobre registro de información</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -22799,7 +25401,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>https://www.prototipos-sicc.com/app/barrios_vivos/explorar</t>
+          <t>https://drive.google.com/file/d/1gbIyrWH8cK07q00yoPBs9D8IWYNv4P2I/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22809,12 +25411,12 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Tablero de seguimiento</t>
+          <t>Prototipo para registro</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -22824,7 +25426,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>https://lookerstudio.google.com/reporting/a1e266a6-ed1a-4500-8776-58e82d1d7746/page/p_pjg06p6njd</t>
+          <t>https://www.prototipos-sicc.com/app/barrios_vivos/explorar</t>
         </is>
       </c>
     </row>
@@ -22834,12 +25436,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Audiovisual</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Vídeo tutoriales para registro</t>
+          <t>Tablero de seguimiento</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -22849,22 +25451,22 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1Cuy0w3cr883zTx_4X1n4TquCUCnheBRm</t>
+          <t>https://lookerstudio.google.com/reporting/a1e266a6-ed1a-4500-8776-58e82d1d7746/page/p_pjg06p6njd</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Audiovisual</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Vídeo tutoriales para registro</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -22874,13 +25476,13 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1f6sPy_pAB5aZpB_kvra4Qy4YiKsiGjgR/view?usp=drive_link</t>
+          <t>https://drive.google.com/drive/folders/1Cuy0w3cr883zTx_4X1n4TquCUCnheBRm</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
@@ -22899,7 +25501,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>https://docs.google.com/presentation/d/1BogTIIMdH15s1-pa4Z9qN-RIW_VTct_g/edit?slide=id.p1#slide=id.p1</t>
+          <t>https://drive.google.com/file/d/1f6sPy_pAB5aZpB_kvra4Qy4YiKsiGjgR/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -22909,12 +25511,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Anexo resultados comparativos</t>
+          <t>Presentación final</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -22924,22 +25526,22 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/11YGZTE7pzMI4lDBZmvYiq5Xq9TwCE1z4/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
+          <t>https://docs.google.com/presentation/d/1BogTIIMdH15s1-pa4Z9qN-RIW_VTct_g/edit?slide=id.p1#slide=id.p1</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Infografía</t>
+          <t>Anexo</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Anexo resultados comparativos</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -22949,7 +25551,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VhroKpPxgqcqQso3fwqBLmJ5zbwmJ8od/view?usp=share_link</t>
+          <t>https://docs.google.com/spreadsheets/d/11YGZTE7pzMI4lDBZmvYiq5Xq9TwCE1z4/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -22959,20 +25561,24 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Infografía</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Diseño de experimento económico</t>
+          <t>Presentación final</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E693" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1VhroKpPxgqcqQso3fwqBLmJ5zbwmJ8od/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -22980,12 +25586,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Cálculo de consumo de agua en ducha por factura</t>
+          <t>Diseño de experimento económico</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -23001,12 +25607,12 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Datos EAAB por Barrio para experimento</t>
+          <t>Cálculo de consumo de agua en ducha por factura</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -23022,12 +25628,12 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Infografía</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Datos de hitos Barrios Vivos Agua</t>
+          <t>Datos EAAB por Barrio para experimento</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -23043,12 +25649,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Infografía</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Cronograma Investigación Agua</t>
+          <t>Datos de hitos Barrios Vivos Agua</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -23060,28 +25666,24 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Cronograma Investigación Agua</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1KnbyFYzDxdGfLHJqZDXjhrrUnvwF8O0D/view?usp=share_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -23089,20 +25691,24 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Informe cuantitativo</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Tablas de salida</t>
+          <t>Presentación final</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E699" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1KnbyFYzDxdGfLHJqZDXjhrrUnvwF8O0D/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -23110,17 +25716,17 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Carpeta archivos</t>
+          <t>Informe cuantitativo</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>ICC Distritos Creativos 2025</t>
+          <t>Tablas de salida</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E700" t="inlineStr"/>
@@ -23131,12 +25737,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Carpeta archivos</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Formulario ICC Distritos Creativos 2025</t>
+          <t>ICC Distritos Creativos 2025</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -23152,58 +25758,54 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Instrumento recolección</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Cronograma ICC Distritos Creativos</t>
+          <t>Formulario ICC Distritos Creativos 2025</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Informe de caracterización con fuentes secundarias</t>
+          <t>Cronograma ICC Distritos Creativos</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E703" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1nqXIcpjznaD1Dn8fjBR_fg7L2XdFwKsg/view?usp=share_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tablero de recorrido por espacio púbilco del centro </t>
+          <t>Informe de caracterización con fuentes secundarias</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -23213,7 +25815,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>https://sdcrd.maps.arcgis.com/apps/dashboards/f5ba03060ca94dfa8d4fee25f0de6d7f</t>
+          <t>https://drive.google.com/file/d/1nqXIcpjznaD1Dn8fjBR_fg7L2XdFwKsg/view?usp=share_link</t>
         </is>
       </c>
     </row>
@@ -23223,7 +25825,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -23233,14 +25835,18 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E705" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>https://sdcrd.maps.arcgis.com/apps/dashboards/f5ba03060ca94dfa8d4fee25f0de6d7f</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
@@ -23249,19 +25855,15 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Informe final</t>
+          <t xml:space="preserve">Tablero de recorrido por espacio púbilco del centro </t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E706" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1NsVGUlWsADXoKnEO31ub8Cp0Krp9Aig3/view?usp=drive_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -23269,12 +25871,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Anexo de definición</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -23284,7 +25886,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1yZIHrgUGq2Lu0TFlzzyGvCS7RXjuxd1M/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1NsVGUlWsADXoKnEO31ub8Cp0Krp9Aig3/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -23294,12 +25896,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Anexo</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Formulario sondeo</t>
+          <t>Anexo de definición</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -23309,7 +25911,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AVJBnJQld7Uyna3WW04TEPkFOQQqFlQl/view?usp=drive_link</t>
+          <t>https://drive.google.com/file/d/1yZIHrgUGq2Lu0TFlzzyGvCS7RXjuxd1M/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -23317,10 +25919,26 @@
       <c r="A709" t="n">
         <v>128</v>
       </c>
-      <c r="B709" t="inlineStr"/>
-      <c r="C709" t="inlineStr"/>
-      <c r="D709" t="inlineStr"/>
-      <c r="E709" t="inlineStr"/>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Formulario sondeo</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1AVJBnJQld7Uyna3WW04TEPkFOQQqFlQl/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -23342,28 +25960,12 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>129</v>
-      </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Informe final</t>
-        </is>
-      </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Análisis de impacto de la implementación de los Laboratorios de Bienestar a adolescentes: Comparación de encuestas pre y post de la implementación del laboratorio: “El Viaje Hacia Dentro de Mi” - Estrategia EstarBien Bogotá </t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E712" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1R8tXuWA5XQrs_U1P2LAakV8WjHZp-Hyc/view?usp=share_link</t>
-        </is>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B712" t="inlineStr"/>
+      <c r="C712" t="inlineStr"/>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -23371,58 +25973,58 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Plan de trabajo</t>
+          <t>Informe final</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Plan de investigación</t>
+          <t xml:space="preserve">Análisis de impacto de la implementación de los Laboratorios de Bienestar a adolescentes: Comparación de encuestas pre y post de la implementación del laboratorio: “El Viaje Hacia Dentro de Mi” - Estrategia EstarBien Bogotá </t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1R8tXuWA5XQrs_U1P2LAakV8WjHZp-Hyc/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Plan de trabajo</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Matriz de preguntas de la EBC</t>
+          <t>Plan de investigación</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Presentación final</t>
+          <t>Tabero de Resultados</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -23432,13 +26034,13 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ez5bU0fGKborxl5_zyUc27muZZizMtFC/view?usp=share_link</t>
+          <t>https://observatoriocultura.github.io/observatorio/#/ebc/encuesta-cultura-ciudadana-2025</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
@@ -23447,69 +26049,41 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Encuesta de recolección de fuentes primarias</t>
+          <t>Matriz de preguntas de la EBC</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E716" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>132</v>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>Informe final</t>
-        </is>
-      </c>
-      <c r="C717" t="inlineStr">
-        <is>
-          <t>Cultura Metro - Estado del Arte</t>
-        </is>
-      </c>
-      <c r="D717" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E717" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/document/d/1TvqbXkunNvyWYuMDu2TZ_rwJeAI2fjFR/edit?usp=sharing&amp;ouid=100772003525119686921&amp;rtpof=true&amp;sd=true</t>
-        </is>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="B717" t="inlineStr"/>
+      <c r="C717" t="inlineStr"/>
+      <c r="D717" t="inlineStr"/>
+      <c r="E717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>133</v>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Presentación Final </t>
-        </is>
-      </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/16AYD-Y9HF8O45rYDxH6a_pgEbUjv_Ofo/view?usp=drive_link</t>
-        </is>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="B718" t="inlineStr"/>
+      <c r="C718" t="inlineStr"/>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr"/>
@@ -23518,258 +26092,363 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>134</v>
-      </c>
-      <c r="B720" t="inlineStr"/>
-      <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
-      <c r="E720" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Presentación</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Presentación final</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Ez5bU0fGKborxl5_zyUc27muZZizMtFC/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>134</v>
-      </c>
-      <c r="B721" t="inlineStr"/>
-      <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Encuesta de recolección de fuentes primarias</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>134</v>
-      </c>
-      <c r="B722" t="inlineStr"/>
-      <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Informe final</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Cultura Metro - Estado del Arte</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1TvqbXkunNvyWYuMDu2TZ_rwJeAI2fjFR/edit?usp=sharing&amp;ouid=100772003525119686921&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>134</v>
-      </c>
-      <c r="B723" t="inlineStr"/>
-      <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr"/>
-      <c r="E723" t="inlineStr"/>
+        <v>133</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Presentación</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presentación Final </t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16AYD-Y9HF8O45rYDxH6a_pgEbUjv_Ofo/view?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
         <v>134</v>
       </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>Visualización</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>Tablero invitados ECCI 2025 - Seguimiento</t>
-        </is>
-      </c>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E724" t="inlineStr">
-        <is>
-          <t>https://lookerstudio.google.com/reporting/49195a24-bd9a-4773-af8a-966bb697f78b/page/p_pjg06p6njd</t>
-        </is>
-      </c>
+      <c r="B724" t="inlineStr"/>
+      <c r="C724" t="inlineStr"/>
+      <c r="D724" t="inlineStr"/>
+      <c r="E724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>135</v>
-      </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>Informe final</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>Marco conceptual</t>
-        </is>
-      </c>
-      <c r="D725" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E725" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/12I-YN44-_0suC2dpHX3vOLYgHwHTHA-E/view?usp=share_link</t>
-        </is>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B725" t="inlineStr"/>
+      <c r="C725" t="inlineStr"/>
+      <c r="D725" t="inlineStr"/>
+      <c r="E725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>135</v>
-      </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>Instrumento recolección</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t xml:space="preserve">índice de reconciliación y paz </t>
-        </is>
-      </c>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E726" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ySdEC1LyX43LPMZdqi2vBiSWXoQRieJH/view?usp=share_link</t>
-        </is>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B726" t="inlineStr"/>
+      <c r="C726" t="inlineStr"/>
+      <c r="D726" t="inlineStr"/>
+      <c r="E726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="n">
+        <v>134</v>
+      </c>
+      <c r="B727" t="inlineStr"/>
+      <c r="C727" t="inlineStr"/>
+      <c r="D727" t="inlineStr"/>
+      <c r="E727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>134</v>
+      </c>
+      <c r="B728" t="inlineStr"/>
+      <c r="C728" t="inlineStr"/>
+      <c r="D728" t="inlineStr"/>
+      <c r="E728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>134</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Visualización</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Tablero invitados ECCI 2025 - Seguimiento</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>https://lookerstudio.google.com/reporting/49195a24-bd9a-4773-af8a-966bb697f78b/page/p_pjg06p6njd</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>135</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Informe final</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Marco conceptual</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12I-YN44-_0suC2dpHX3vOLYgHwHTHA-E/view?usp=share_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>135</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t xml:space="preserve">índice de reconciliación y paz </t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ySdEC1LyX43LPMZdqi2vBiSWXoQRieJH/view?usp=share_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
         <v>136</v>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>Informe final</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento Desarrollo Técnico Normativo y misional del enfoque de Cultura Ciudadana para la movilidad
 </t>
         </is>
       </c>
-      <c r="D727" t="inlineStr">
+      <c r="D732" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr"/>
-    </row>
-    <row r="728">
-      <c r="A728" t="n">
+      <c r="E732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
         <v>136</v>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>Informe final</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t xml:space="preserve">Estado del arte y de la práctica sobre problemáticas relacionadas a cultura ciudadana y movilidad 
 </t>
         </is>
       </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1l3CBDIXbCVbiG153wP35kkD4Q44DZbI1/view?usp=share_link</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="n">
+    <row r="734">
+      <c r="A734" t="n">
         <v>136</v>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>Mapa/Geovisor</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>Geovisor Movilidad</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr">
+      <c r="D734" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E729" t="inlineStr">
+      <c r="E734" t="inlineStr">
         <is>
           <t>https://www.arcgis.com/apps/dashboards/3a8a858de18047528174d7bc158b4b42</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="n">
+    <row r="735">
+      <c r="A735" t="n">
         <v>137</v>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>Informe final</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>Informe final de mediciones</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E730" t="inlineStr">
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1liHn1t_9w1D5ry0UIfT6kxLszVuyErB_/view?usp=drive_link</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="n">
+    <row r="736">
+      <c r="A736" t="n">
         <v>137</v>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>Visualización</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>Tablero de resultados</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E731" t="inlineStr">
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/view?r=eyJrIjoiOWYwOThhMjMtOTBjZC00ZGY5LThhYjktMTY5OWYzYWI0ZDJjIiwidCI6IjRmNzkzOWM3LWFhNjAtNDliZC05YjdiLTZmODFjMzdkMWIzNyJ9&amp;pageName=ef377ed828063259b15e</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="n">
+    <row r="737">
+      <c r="A737" t="n">
         <v>137</v>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>Base de datos</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>Datos de encuestas</t>
         </is>
       </c>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1rX2RfuDon4SukoBpHxRg7m9fnL6_1Jw2/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
         </is>

--- a/content/data/investigaciones/investigaciones.xlsx
+++ b/content/data/investigaciones/investigaciones.xlsx
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -26044,12 +26044,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Matriz de preguntas de la EBC</t>
+          <t>Presentación resumen de resultados</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
+          <t>https://docs.google.com/presentation/d/1bPLTlrkQNn8G8vEepHLs5l3QTNfF8usV/edit?slide=id.p1#slide=id.p1</t>
         </is>
       </c>
     </row>
@@ -26067,10 +26067,26 @@
       <c r="A717" t="n">
         <v>130</v>
       </c>
-      <c r="B717" t="inlineStr"/>
-      <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Matriz de preguntas de la EBC</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">

--- a/content/data/investigaciones/investigaciones.xlsx
+++ b/content/data/investigaciones/investigaciones.xlsx
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>https://docs.google.com/presentation/d/1bPLTlrkQNn8G8vEepHLs5l3QTNfF8usV/edit?slide=id.p1#slide=id.p1</t>
+          <t>https://docs.google.com/presentation/d/1eq2OlrJJGnYvh_AV6hq9vvACrpBeUkTo/edit?slide=id.p1#slide=id.p1</t>
         </is>
       </c>
     </row>

--- a/content/data/investigaciones/investigaciones.xlsx
+++ b/content/data/investigaciones/investigaciones.xlsx
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -26019,12 +26019,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Visualización</t>
+          <t>Presentación</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Tabero de Resultados</t>
+          <t>Presentación resumen de resultados</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>https://observatoriocultura.github.io/observatorio/#/ebc/encuesta-cultura-ciudadana-2025</t>
+          <t>https://docs.google.com/presentation/d/1eq2OlrJJGnYvh_AV6hq9vvACrpBeUkTo/edit?slide=id.p1#slide=id.p1</t>
         </is>
       </c>
     </row>
@@ -26044,12 +26044,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Presentación</t>
+          <t>Visualización</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Presentación resumen de resultados</t>
+          <t>Tabero de Resultados</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>https://docs.google.com/presentation/d/1eq2OlrJJGnYvh_AV6hq9vvACrpBeUkTo/edit?slide=id.p1#slide=id.p1</t>
+          <t>https://observatoriocultura.github.io/observatorio/#/ebc/encuesta-cultura-ciudadana-2025</t>
         </is>
       </c>
     </row>
@@ -26069,12 +26069,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Instrumento recolección</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Matriz de preguntas de la EBC</t>
+          <t>Datos detallados de respuestas</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
+          <t>https://docs.google.com/spreadsheets/d/1nCsuCpG7YJ-PQ7ilHtNdGahIDfNHcHDT/edit?usp=drive_link&amp;ouid=114299960211627169695&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
     </row>
@@ -26092,10 +26092,26 @@
       <c r="A718" t="n">
         <v>130</v>
       </c>
-      <c r="B718" t="inlineStr"/>
-      <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
-      <c r="E718" t="inlineStr"/>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Instrumento recolección</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Matriz de preguntas de la EBC</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1DBDvo9ZxCKI-N5iG-XNns-ILD2S1UEMe/view?usp=share_link</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
